--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 00:14:23</t>
+          <t>2026-06-29 02:21:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.02</v>
+        <v>2.12</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>2.56</v>
       </c>
       <c r="H2" t="n">
-        <v>1.02</v>
+        <v>2.86</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>3.15</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 02:21:25</t>
+          <t>2026-06-29 04:28:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 04:28:19</t>
+          <t>2026-06-29 06:35:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -869,7 +869,7 @@
         <v>4.3</v>
       </c>
       <c r="J2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
         <v>4.9</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 06:35:13</t>
+          <t>2026-06-29 08:42:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -863,16 +863,16 @@
         <v>2.56</v>
       </c>
       <c r="H2" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I2" t="n">
         <v>4.3</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="K2" t="n">
-        <v>4.9</v>
+        <v>100</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -890,7 +890,7 @@
         <v>1.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 08:42:13</t>
+          <t>2026-06-29 10:49:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -863,28 +863,28 @@
         <v>2.56</v>
       </c>
       <c r="H2" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="I2" t="n">
         <v>4.3</v>
       </c>
       <c r="J2" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="K2" t="n">
-        <v>100</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P2" t="n">
         <v>1.85</v>
@@ -893,184 +893,184 @@
         <v>1.89</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 10:49:32</t>
+          <t>2026-06-29 12:56:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,7 +860,7 @@
         <v>2.12</v>
       </c>
       <c r="G2" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="H2" t="n">
         <v>3.05</v>
@@ -869,10 +869,10 @@
         <v>4.3</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.36</v>
@@ -881,7 +881,7 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O2" t="n">
         <v>1.32</v>
@@ -890,7 +890,7 @@
         <v>1.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="R2" t="n">
         <v>1.33</v>
@@ -899,7 +899,7 @@
         <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="U2" t="n">
         <v>2.06</v>
@@ -908,13 +908,13 @@
         <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X2" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
         <v>30</v>
@@ -923,22 +923,22 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD2" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
         <v>55</v>
       </c>
       <c r="AF2" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
         <v>21</v>
@@ -965,70 +965,70 @@
         <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1040,7 +1040,7 @@
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
@@ -1058,7 +1058,7 @@
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,515 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 12:56:33</t>
+          <t>2026-06-29 15:03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Forge</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Vancouver FC</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="X3" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-06-29 15:03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Eskilsminne</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Kristianstads</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-06-29 15:03:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,28 +860,28 @@
         <v>2.12</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="H2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I2" t="n">
         <v>4.3</v>
       </c>
       <c r="J2" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.32</v>
@@ -890,13 +890,13 @@
         <v>1.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="R2" t="n">
         <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T2" t="n">
         <v>1.75</v>
@@ -908,7 +908,7 @@
         <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -971,7 +971,7 @@
         <v>3.9</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="AS2" t="n">
         <v>3.35</v>
@@ -986,7 +986,7 @@
         <v>4</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="AX2" t="n">
         <v>3.95</v>
@@ -995,28 +995,28 @@
         <v>3.7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="BE2" t="n">
         <v>3.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 15:03:30</t>
+          <t>2026-06-29 17:10:34</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
         <v>5.1</v>
@@ -1144,13 +1144,13 @@
         <v>1.97</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R3" t="n">
         <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="T3" t="n">
         <v>1.94</v>
@@ -1177,7 +1177,7 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC3" t="n">
         <v>12.5</v>
@@ -1219,58 +1219,58 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BF3" t="n">
         <v>6</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH3" t="n">
         <v>3.8</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 15:03:30</t>
+          <t>2026-06-29 17:10:34</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,1277 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 15:03:30</t>
+          <t>2026-06-29 17:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Tecnico Universitario</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-06-29 17:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Delfin</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Emelec</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-06-29 17:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Barcelona (Ecu)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-29 17:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CD Leones del Norte</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-29 17:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LDU</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>11</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-29 17:10:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -896,7 +896,7 @@
         <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="T2" t="n">
         <v>1.75</v>
@@ -965,55 +965,55 @@
         <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="AT2" t="n">
         <v>3.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AV2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AW2" t="n">
         <v>4.7</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BB2" t="n">
         <v>4.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BD2" t="n">
         <v>4.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BG2" t="n">
         <v>4.7</v>
@@ -1028,7 +1028,7 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1040,7 +1040,7 @@
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
@@ -1058,7 +1058,7 @@
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 17:10:34</t>
+          <t>2026-06-29 19:17:42</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
         <v>5.1</v>
@@ -1138,22 +1138,22 @@
         <v>3.75</v>
       </c>
       <c r="O3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R3" t="n">
         <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U3" t="n">
         <v>1.83</v>
@@ -1177,7 +1177,7 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC3" t="n">
         <v>12.5</v>
@@ -1189,7 +1189,7 @@
         <v>150</v>
       </c>
       <c r="AF3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG3" t="n">
         <v>12</v>
@@ -1219,58 +1219,58 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW3" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU3" t="n">
+      <c r="AX3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AY3" t="n">
         <v>3.5</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>4.1</v>
       </c>
-      <c r="AW3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4</v>
-      </c>
       <c r="BA3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BF3" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BH3" t="n">
         <v>3.8</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 17:10:34</t>
+          <t>2026-06-29 19:17:42</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 17:10:34</t>
+          <t>2026-06-29 19:17:42</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-29 17:10:34</t>
+          <t>2026-06-29 19:17:42</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-29 17:10:34</t>
+          <t>2026-06-29 19:17:42</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-29 17:10:34</t>
+          <t>2026-06-29 19:17:42</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-29 17:10:34</t>
+          <t>2026-06-29 19:17:42</t>
         </is>
       </c>
     </row>
@@ -2641,224 +2641,224 @@
         <v>1.58</v>
       </c>
       <c r="H9" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="I9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="K9" t="n">
         <v>4.7</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
         <v>1.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-29 17:10:34</t>
+          <t>2026-06-29 19:17:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1058,7 +1058,7 @@
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 19:17:42</t>
+          <t>2026-06-29 21:24:22</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
         <v>5.1</v>
@@ -1150,7 +1150,7 @@
         <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="T3" t="n">
         <v>1.95</v>
@@ -1246,7 +1246,7 @@
         <v>3.3</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AZ3" t="n">
         <v>4.1</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 19:17:42</t>
+          <t>2026-06-29 21:24:22</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 19:17:42</t>
+          <t>2026-06-29 21:24:22</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1655,7 +1655,7 @@
         <v>1.01</v>
       </c>
       <c r="R5" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="S5" t="n">
         <v>1.01</v>
@@ -1727,52 +1727,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-29 19:17:42</t>
+          <t>2026-06-29 21:24:22</t>
         </is>
       </c>
     </row>
@@ -1859,189 +1859,189 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>1.58</v>
       </c>
       <c r="H6" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="R6" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK6" t="n">
         <v>1.01</v>
@@ -2053,13 +2053,13 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BQ6" t="n">
         <v>1.01</v>
@@ -2071,7 +2071,7 @@
         <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU6" t="n">
         <v>1.01</v>
@@ -2089,776 +2089,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA6" t="n">
         <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-29 19:17:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Ecuadorian Serie A</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>17:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Barcelona (Ecu)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Deportivo Cuenca</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-06-29 19:17:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Ecuadorian Serie A</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>17:00:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Libertad FC</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CD Leones del Norte</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>2026-06-29 19:17:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Ecuadorian Serie A</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LDU</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Orense Sporting Club</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I9" t="n">
-        <v>9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>22</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>22</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>22</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>21</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>2026-06-29 19:17:42</t>
+          <t>2026-06-29 21:24:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -1028,7 +1028,7 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1040,7 +1040,7 @@
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 21:24:22</t>
+          <t>2026-06-29 23:30:59</t>
         </is>
       </c>
     </row>
@@ -1111,64 +1111,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="G3" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.75</v>
+        <v>2.92</v>
       </c>
       <c r="O3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.28</v>
       </c>
-      <c r="P3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.37</v>
-      </c>
       <c r="S3" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="T3" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="V3" t="n">
         <v>1.11</v>
       </c>
       <c r="W3" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="n">
         <v>85</v>
@@ -1177,19 +1177,19 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD3" t="n">
         <v>36</v>
       </c>
       <c r="AE3" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG3" t="n">
         <v>12</v>
@@ -1198,7 +1198,7 @@
         <v>30</v>
       </c>
       <c r="AI3" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AJ3" t="n">
         <v>16.5</v>
@@ -1207,19 +1207,19 @@
         <v>20</v>
       </c>
       <c r="AL3" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AQ3" t="n">
         <v>4.1</v>
@@ -1234,55 +1234,55 @@
         <v>3.05</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AW3" t="n">
         <v>4.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AY3" t="n">
         <v>3.45</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA3" t="n">
         <v>4.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE3" t="n">
         <v>4.7</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.8</v>
+        <v>3.55</v>
       </c>
       <c r="BG3" t="n">
         <v>4.7</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1291,22 +1291,22 @@
         <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 21:24:22</t>
+          <t>2026-06-29 23:30:59</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
         <v>1.09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 21:24:22</t>
+          <t>2026-06-29 23:30:59</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-29 21:24:22</t>
+          <t>2026-06-29 23:30:59</t>
         </is>
       </c>
     </row>
@@ -1879,10 +1879,10 @@
         <v>1.58</v>
       </c>
       <c r="H6" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="I6" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="J6" t="n">
         <v>4.1</v>
@@ -1891,7 +1891,7 @@
         <v>4.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1921,13 +1921,13 @@
         <v>1.76</v>
       </c>
       <c r="V6" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W6" t="n">
         <v>2.72</v>
       </c>
       <c r="X6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y6" t="n">
         <v>28</v>
@@ -1951,7 +1951,7 @@
         <v>180</v>
       </c>
       <c r="AF6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG6" t="n">
         <v>12.5</v>
@@ -1963,7 +1963,7 @@
         <v>160</v>
       </c>
       <c r="AJ6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AK6" t="n">
         <v>22</v>
@@ -1978,79 +1978,79 @@
         <v>11</v>
       </c>
       <c r="AO6" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AP6" t="n">
-        <v>10.5</v>
+        <v>3.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>19.5</v>
+        <v>3.9</v>
       </c>
       <c r="AR6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD6" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>36</v>
-      </c>
       <c r="BE6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH6" t="n">
         <v>3.45</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="BJ6" t="n">
         <v>12</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BN6" t="n">
         <v>3.9</v>
@@ -2062,41 +2062,41 @@
         <v>10</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BT6" t="n">
         <v>11.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>21</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-29 21:24:22</t>
+          <t>2026-06-29 23:30:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -860,19 +860,19 @@
         <v>2.12</v>
       </c>
       <c r="G2" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.4</v>
@@ -881,16 +881,16 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O2" t="n">
         <v>1.32</v>
       </c>
       <c r="P2" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R2" t="n">
         <v>1.33</v>
@@ -908,7 +908,7 @@
         <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -968,7 +968,7 @@
         <v>3.85</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AR2" t="n">
         <v>4.3</v>
@@ -980,25 +980,25 @@
         <v>3.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AY2" t="n">
         <v>3.65</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB2" t="n">
         <v>4.4</v>
@@ -1007,7 +1007,7 @@
         <v>4.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE2" t="n">
         <v>4.8</v>
@@ -1016,7 +1016,7 @@
         <v>4.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1028,7 +1028,7 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1040,7 +1040,7 @@
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
@@ -1058,7 +1058,7 @@
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 23:30:59</t>
+          <t>2026-06-30 01:37:33</t>
         </is>
       </c>
     </row>
@@ -1111,64 +1111,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="G3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I3" t="n">
         <v>10.5</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="R3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="V3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W3" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Z3" t="n">
         <v>85</v>
@@ -1177,49 +1177,49 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC3" t="n">
         <v>11.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI3" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ3" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AQ3" t="n">
         <v>4.1</v>
@@ -1231,22 +1231,22 @@
         <v>4.7</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AV3" t="n">
         <v>4.3</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.25</v>
+        <v>6.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>4.2</v>
@@ -1255,10 +1255,10 @@
         <v>4.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BD3" t="n">
         <v>4.4</v>
@@ -1267,22 +1267,22 @@
         <v>4.7</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BG3" t="n">
         <v>4.7</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1291,22 +1291,22 @@
         <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 23:30:59</t>
+          <t>2026-06-30 01:37:33</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
         <v>1.18</v>
       </c>
       <c r="R4" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="S4" t="n">
         <v>1.19</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 23:30:59</t>
+          <t>2026-06-30 01:37:33</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-29 23:30:59</t>
+          <t>2026-06-30 01:37:33</t>
         </is>
       </c>
     </row>
@@ -1879,10 +1879,10 @@
         <v>1.58</v>
       </c>
       <c r="H6" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="I6" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="J6" t="n">
         <v>4.1</v>
@@ -1915,19 +1915,19 @@
         <v>3.55</v>
       </c>
       <c r="T6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W6" t="n">
         <v>2.72</v>
       </c>
       <c r="X6" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y6" t="n">
         <v>28</v>
@@ -1936,7 +1936,7 @@
         <v>90</v>
       </c>
       <c r="AA6" t="n">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="AB6" t="n">
         <v>8.6</v>
@@ -1963,7 +1963,7 @@
         <v>160</v>
       </c>
       <c r="AJ6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK6" t="n">
         <v>22</v>
@@ -1975,64 +1975,64 @@
         <v>220</v>
       </c>
       <c r="AN6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.6</v>
+        <v>12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.9</v>
+        <v>16.5</v>
       </c>
       <c r="AR6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS6" t="n">
         <v>4.3</v>
       </c>
-      <c r="AS6" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AT6" t="n">
-        <v>3</v>
+        <v>6.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.3</v>
+        <v>8.6</v>
       </c>
       <c r="AV6" t="n">
         <v>4</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.15</v>
+        <v>7.2</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.35</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.6</v>
+        <v>11.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.75</v>
+        <v>15</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.2</v>
+        <v>36</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH6" t="n">
         <v>3.45</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-29 23:30:59</t>
+          <t>2026-06-30 01:37:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -860,19 +860,19 @@
         <v>2.12</v>
       </c>
       <c r="G2" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J2" t="n">
         <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
         <v>1.4</v>
@@ -881,13 +881,13 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.32</v>
       </c>
       <c r="P2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q2" t="n">
         <v>1.95</v>
@@ -908,7 +908,7 @@
         <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -941,7 +941,7 @@
         <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AI2" t="n">
         <v>65</v>
@@ -971,52 +971,52 @@
         <v>3.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.7</v>
+        <v>2.22</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.6</v>
+        <v>2.56</v>
       </c>
       <c r="AX2" t="n">
         <v>3.85</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.7</v>
+        <v>2.58</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.5</v>
+        <v>2.54</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.8</v>
+        <v>2.26</v>
       </c>
       <c r="BF2" t="n">
         <v>4.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.6</v>
+        <v>2.56</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1040,7 +1040,7 @@
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 01:37:33</t>
+          <t>2026-06-30 03:44:12</t>
         </is>
       </c>
     </row>
@@ -1111,58 +1111,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="G3" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I3" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O3" t="n">
         <v>1.39</v>
       </c>
-      <c r="M3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.33</v>
-      </c>
       <c r="P3" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="V3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W3" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="X3" t="n">
         <v>18.5</v>
@@ -1177,112 +1177,112 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC3" t="n">
         <v>11.5</v>
       </c>
       <c r="AD3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH3" t="n">
         <v>38</v>
       </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>32</v>
-      </c>
       <c r="AI3" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AR3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS3" t="n">
         <v>4.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4.7</v>
       </c>
       <c r="AT3" t="n">
         <v>3</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.6</v>
+        <v>3.15</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AZ3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD3" t="n">
         <v>4.2</v>
       </c>
-      <c r="BA3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD3" t="n">
+      <c r="BE3" t="n">
         <v>4.4</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>4.7</v>
       </c>
       <c r="BF3" t="n">
         <v>3.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1291,22 +1291,22 @@
         <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 01:37:33</t>
+          <t>2026-06-30 03:44:12</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 01:37:33</t>
+          <t>2026-06-30 03:44:12</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 01:37:33</t>
+          <t>2026-06-30 03:44:12</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
         <v>7.6</v>
       </c>
       <c r="I6" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J6" t="n">
         <v>4.1</v>
@@ -1897,19 +1897,19 @@
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.33</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.32</v>
       </c>
       <c r="S6" t="n">
         <v>3.55</v>
@@ -1921,13 +1921,13 @@
         <v>1.77</v>
       </c>
       <c r="V6" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W6" t="n">
         <v>2.72</v>
       </c>
       <c r="X6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y6" t="n">
         <v>28</v>
@@ -1990,7 +1990,7 @@
         <v>4.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT6" t="n">
         <v>6.2</v>
@@ -2032,7 +2032,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH6" t="n">
         <v>3.45</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-30 01:37:33</t>
+          <t>2026-06-30 03:44:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,7 +866,7 @@
         <v>3.4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="J2" t="n">
         <v>3.3</v>
@@ -905,10 +905,10 @@
         <v>2.06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -965,61 +965,61 @@
         <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.35</v>
+        <v>2.22</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.22</v>
+        <v>1.93</v>
       </c>
       <c r="AT2" t="n">
         <v>3.95</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.26</v>
+        <v>1.94</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BI2" t="n">
         <v>2.78</v>
@@ -1028,49 +1028,49 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 03:44:12</t>
+          <t>2026-06-30 05:51:04</t>
         </is>
       </c>
     </row>
@@ -1111,58 +1111,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="G3" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="H3" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="I3" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>2.76</v>
+        <v>3.35</v>
       </c>
       <c r="O3" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="R3" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="X3" t="n">
         <v>18.5</v>
@@ -1171,118 +1171,118 @@
         <v>29</v>
       </c>
       <c r="Z3" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG3" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>13</v>
-      </c>
       <c r="AH3" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ3" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN3" t="n">
-        <v>15.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU3" t="n">
         <v>3.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.15</v>
       </c>
       <c r="AV3" t="n">
         <v>4.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>4.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB3" t="n">
         <v>3.7</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.46</v>
+        <v>2.86</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1291,28 +1291,28 @@
         <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BO3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 03:44:12</t>
+          <t>2026-06-30 05:51:04</t>
         </is>
       </c>
     </row>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 03:44:12</t>
+          <t>2026-06-30 05:51:04</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>HFX Wanderers</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Atletico Ottawa</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="R5" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 03:44:12</t>
+          <t>2026-06-30 05:51:04</t>
         </is>
       </c>
     </row>
@@ -1859,244 +1859,498 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CD Leones del Norte</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-06-30 05:51:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>LDU</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Orense Sporting Club</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F7" t="n">
         <v>1.49</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G7" t="n">
         <v>1.58</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H7" t="n">
         <v>7.6</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>4.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K7" t="n">
         <v>4.7</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L7" t="n">
         <v>1.41</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M7" t="n">
         <v>1.07</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="X7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>180</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>270</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH7" t="n">
         <v>3.45</v>
       </c>
-      <c r="O6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="X6" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>28</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>350</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="BI7" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BJ7" t="n">
         <v>12</v>
       </c>
-      <c r="AD6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>180</v>
-      </c>
-      <c r="AF6" t="n">
+      <c r="BK7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP7" t="n">
         <v>10</v>
       </c>
-      <c r="AG6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN6" t="n">
+      <c r="BQ7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT7" t="n">
         <v>11.5</v>
       </c>
-      <c r="AO6" t="n">
-        <v>270</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT6" t="n">
+      <c r="BU7" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB6" t="n">
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
         <v>11.5</v>
       </c>
-      <c r="BC6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF6" t="n">
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>21</v>
+      </c>
+      <c r="CA7" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BG6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>21</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-06-30 03:44:12</t>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-30 05:51:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -869,7 +869,7 @@
         <v>3.95</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
         <v>3.85</v>
@@ -950,7 +950,7 @@
         <v>34</v>
       </c>
       <c r="AK2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL2" t="n">
         <v>46</v>
@@ -965,61 +965,61 @@
         <v>55</v>
       </c>
       <c r="AP2" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV2" t="n">
         <v>4</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AT2" t="n">
+      <c r="AW2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AX2" t="n">
         <v>3.95</v>
       </c>
-      <c r="AU2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AY2" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.32</v>
+        <v>3.05</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.24</v>
+        <v>2.96</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.94</v>
+        <v>3.15</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.4</v>
+        <v>2.82</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="BH2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BI2" t="n">
         <v>2.78</v>
@@ -1028,13 +1028,13 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
@@ -1046,13 +1046,13 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
@@ -1064,13 +1064,13 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 05:51:04</t>
+          <t>2026-06-30 07:57:45</t>
         </is>
       </c>
     </row>
@@ -1111,67 +1111,67 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="G3" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="H3" t="n">
         <v>5.9</v>
       </c>
       <c r="I3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
         <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="X3" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Z3" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1180,109 +1180,109 @@
         <v>8.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD3" t="n">
         <v>34</v>
       </c>
       <c r="AE3" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AF3" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="AG3" t="n">
         <v>11.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AI3" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AJ3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK3" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AL3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM3" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU3" t="n">
         <v>3.8</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AV3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB3" t="n">
         <v>4.2</v>
       </c>
-      <c r="AW3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BC3" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,19 +1294,19 @@
         <v>4.3</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 05:51:04</t>
+          <t>2026-06-30 07:57:45</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.02</v>
+        <v>1.9</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
@@ -1404,7 +1404,7 @@
         <v>1.07</v>
       </c>
       <c r="S4" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 05:51:04</t>
+          <t>2026-06-30 07:57:45</t>
         </is>
       </c>
     </row>
@@ -1619,178 +1619,178 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="H5" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1</v>
+        <v>3.75</v>
       </c>
       <c r="O5" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1</v>
+        <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.32</v>
+        <v>1.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.08</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>1.32</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1799,50 +1799,50 @@
         <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 05:51:04</t>
+          <t>2026-06-30 07:57:45</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-30 05:51:04</t>
+          <t>2026-06-30 07:57:45</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="G7" t="n">
         <v>1.58</v>
@@ -2136,7 +2136,7 @@
         <v>7.6</v>
       </c>
       <c r="I7" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="J7" t="n">
         <v>4.1</v>
@@ -2172,25 +2172,25 @@
         <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W7" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="X7" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y7" t="n">
         <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AA7" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AB7" t="n">
         <v>8.4</v>
@@ -2205,7 +2205,7 @@
         <v>180</v>
       </c>
       <c r="AF7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG7" t="n">
         <v>12</v>
@@ -2235,43 +2235,43 @@
         <v>270</v>
       </c>
       <c r="AP7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU7" t="n">
         <v>8.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.3</v>
+        <v>24</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC7" t="n">
         <v>15</v>
@@ -2280,16 +2280,16 @@
         <v>36</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI7" t="n">
         <v>2.76</v>
@@ -2298,59 +2298,59 @@
         <v>12</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN7" t="n">
         <v>3.9</v>
       </c>
       <c r="BO7" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="BP7" t="n">
         <v>10</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT7" t="n">
         <v>11.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ7" t="n">
         <v>21</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-30 05:51:04</t>
+          <t>2026-06-30 07:57:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>3.95</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
         <v>3.85</v>
@@ -965,58 +965,58 @@
         <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.68</v>
+        <v>3.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="AT2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY2" t="n">
         <v>3.6</v>
       </c>
-      <c r="AU2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>4</v>
       </c>
-      <c r="AW2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>2.8</v>
-      </c>
       <c r="BA2" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.96</v>
+        <v>4.3</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.15</v>
+        <v>4.7</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.82</v>
+        <v>4</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="BH2" t="n">
         <v>5.7</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 07:57:45</t>
+          <t>2026-06-30 10:04:55</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="G3" t="n">
         <v>1.65</v>
@@ -1135,16 +1135,16 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P3" t="n">
         <v>1.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="R3" t="n">
         <v>1.33</v>
@@ -1153,10 +1153,10 @@
         <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V3" t="n">
         <v>1.13</v>
@@ -1165,7 +1165,7 @@
         <v>2.52</v>
       </c>
       <c r="X3" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y3" t="n">
         <v>23</v>
@@ -1186,7 +1186,7 @@
         <v>34</v>
       </c>
       <c r="AE3" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF3" t="n">
         <v>9.4</v>
@@ -1195,7 +1195,7 @@
         <v>11.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI3" t="n">
         <v>140</v>
@@ -1204,7 +1204,7 @@
         <v>16</v>
       </c>
       <c r="AK3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL3" t="n">
         <v>50</v>
@@ -1213,64 +1213,64 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB3" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR3" t="n">
+      <c r="BC3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE3" t="n">
         <v>5.3</v>
       </c>
-      <c r="AS3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BF3" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BH3" t="n">
         <v>3.9</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 07:57:45</t>
+          <t>2026-06-30 10:04:55</t>
         </is>
       </c>
     </row>
@@ -1371,13 +1371,13 @@
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1401,10 +1401,10 @@
         <v>1.18</v>
       </c>
       <c r="R4" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1416,7 +1416,7 @@
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 07:57:45</t>
+          <t>2026-06-30 10:04:55</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,192 +1605,192 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Haukar</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Atletico Ottawa</t>
+          <t>Kari</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="G5" t="n">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="I5" t="n">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="K5" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>3.75</v>
+        <v>1.08</v>
       </c>
       <c r="O5" t="n">
-        <v>1.27</v>
+        <v>1.05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.97</v>
+        <v>1.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.8</v>
+        <v>1.05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>1.05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1799,57 +1799,57 @@
         <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 07:57:45</t>
+          <t>2026-06-30 10:04:55</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,187 +1864,187 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>HFX Wanderers</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Atletico Ottawa</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="H6" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.97</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2053,50 +2053,50 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-30 07:57:45</t>
+          <t>2026-06-30 10:04:55</t>
         </is>
       </c>
     </row>
@@ -2113,244 +2113,498 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CD Leones del Norte</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-30 10:04:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>LDU</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Orense Sporting Club</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="F8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G8" t="n">
         <v>1.58</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H8" t="n">
         <v>7.6</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="X8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>340</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>180</v>
+      </c>
+      <c r="AF8" t="n">
         <v>10.5</v>
       </c>
-      <c r="J7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="AG8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>270</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS8" t="n">
         <v>4.7</v>
       </c>
-      <c r="L7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>28</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>340</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="AT8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF8" t="n">
         <v>8.4</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="BG8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BJ8" t="n">
         <v>12</v>
       </c>
-      <c r="AD7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>180</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>270</v>
-      </c>
-      <c r="AP7" t="n">
+      <c r="BK8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
         <v>12.5</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
         <v>12.5</v>
       </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ7" t="n">
+      <c r="BZ8" t="n">
         <v>21</v>
       </c>
-      <c r="CA7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-06-30 07:57:45</t>
+      <c r="CA8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-30 10:04:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -881,7 +881,7 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O2" t="n">
         <v>1.32</v>
@@ -902,7 +902,7 @@
         <v>1.75</v>
       </c>
       <c r="U2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V2" t="n">
         <v>1.34</v>
@@ -965,58 +965,58 @@
         <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AR2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4</v>
-      </c>
       <c r="BA2" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.3</v>
+        <v>2.96</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.7</v>
+        <v>3.15</v>
       </c>
       <c r="BF2" t="n">
-        <v>4</v>
+        <v>2.82</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="BH2" t="n">
         <v>5.7</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 10:04:55</t>
+          <t>2026-06-30 12:11:53</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="G3" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="H3" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="I3" t="n">
         <v>8.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.34</v>
@@ -1135,34 +1135,34 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O3" t="n">
         <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="T3" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
         <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="X3" t="n">
         <v>18.5</v>
@@ -1171,13 +1171,13 @@
         <v>23</v>
       </c>
       <c r="Z3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC3" t="n">
         <v>11.5</v>
@@ -1186,7 +1186,7 @@
         <v>34</v>
       </c>
       <c r="AE3" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AF3" t="n">
         <v>9.4</v>
@@ -1204,19 +1204,19 @@
         <v>16</v>
       </c>
       <c r="AK3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AP3" t="n">
         <v>4.2</v>
@@ -1228,13 +1228,13 @@
         <v>5.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="AV3" t="n">
         <v>4.7</v>
@@ -1243,19 +1243,19 @@
         <v>5.3</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.45</v>
+        <v>7.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.7</v>
+        <v>7.8</v>
       </c>
       <c r="AZ3" t="n">
         <v>4.7</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC3" t="n">
         <v>4.4</v>
@@ -1267,7 +1267,7 @@
         <v>5.3</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG3" t="n">
         <v>5.3</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 10:04:55</t>
+          <t>2026-06-30 12:11:53</t>
         </is>
       </c>
     </row>
@@ -1389,19 +1389,19 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Q4" t="n">
         <v>1.18</v>
       </c>
       <c r="R4" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="S4" t="n">
         <v>1.19</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 10:04:55</t>
+          <t>2026-06-30 12:11:53</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1727,52 +1727,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 10:04:55</t>
+          <t>2026-06-30 12:11:53</t>
         </is>
       </c>
     </row>
@@ -1873,178 +1873,178 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G6" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="H6" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="I6" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="J6" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="V6" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>19.5</v>
+        <v>14</v>
       </c>
       <c r="Y6" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD6" t="n">
         <v>15.5</v>
       </c>
       <c r="AE6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN6" t="n">
         <v>36</v>
       </c>
-      <c r="AF6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG6" t="n">
+      <c r="AO6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR6" t="n">
         <v>15</v>
       </c>
-      <c r="AH6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AS6" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.75</v>
+        <v>8</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.8</v>
+        <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.85</v>
+        <v>14.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.55</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.75</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.86</v>
+        <v>2.56</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2056,47 +2056,47 @@
         <v>6.2</v>
       </c>
       <c r="BO6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>24</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>16</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>40</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>26</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU6" t="n">
         <v>4.4</v>
       </c>
-      <c r="BP6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BV6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BW6" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BX6" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BY6" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BZ6" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="CA6" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-30 10:04:55</t>
+          <t>2026-06-30 12:11:53</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-30 10:04:55</t>
+          <t>2026-06-30 12:11:53</t>
         </is>
       </c>
     </row>
@@ -2384,64 +2384,64 @@
         <v>1.49</v>
       </c>
       <c r="G8" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I8" t="n">
         <v>9</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.34</v>
       </c>
-      <c r="P8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.33</v>
-      </c>
       <c r="S8" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V8" t="n">
         <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y8" t="n">
         <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AA8" t="n">
         <v>340</v>
@@ -2471,7 +2471,7 @@
         <v>160</v>
       </c>
       <c r="AJ8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AK8" t="n">
         <v>22</v>
@@ -2480,16 +2480,16 @@
         <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN8" t="n">
         <v>11</v>
       </c>
       <c r="AO8" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AP8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ8" t="n">
         <v>19.5</v>
@@ -2498,19 +2498,19 @@
         <v>4.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV8" t="n">
         <v>4.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AX8" t="n">
         <v>7.4</v>
@@ -2519,34 +2519,34 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BB8" t="n">
         <v>12</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.2</v>
+        <v>15.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG8" t="n">
         <v>4.6</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="BJ8" t="n">
         <v>12</v>
@@ -2567,16 +2567,16 @@
         <v>3.05</v>
       </c>
       <c r="BP8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT8" t="n">
         <v>11.5</v>
@@ -2588,23 +2588,23 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ8" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>14.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-30 10:04:55</t>
+          <t>2026-06-30 12:11:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -857,58 +857,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G2" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="H2" t="n">
         <v>3.4</v>
       </c>
       <c r="I2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S2" t="n">
         <v>3.25</v>
       </c>
-      <c r="O2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.15</v>
-      </c>
       <c r="T2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.75</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.73</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -932,7 +932,7 @@
         <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF2" t="n">
         <v>970</v>
@@ -944,7 +944,7 @@
         <v>970</v>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="n">
         <v>34</v>
@@ -953,40 +953,40 @@
         <v>28</v>
       </c>
       <c r="AL2" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AO2" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP2" t="n">
         <v>3.95</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.92</v>
+        <v>4.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT2" t="n">
         <v>3.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AV2" t="n">
         <v>4</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="AX2" t="n">
         <v>3.95</v>
@@ -995,82 +995,82 @@
         <v>3.7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.96</v>
+        <v>4.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.15</v>
+        <v>4.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.82</v>
+        <v>4.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.91</v>
+        <v>5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.06</v>
+        <v>7.2</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.25</v>
+        <v>6.4</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 12:11:53</t>
+          <t>2026-06-30 14:19:19</t>
         </is>
       </c>
     </row>
@@ -1111,40 +1111,40 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I3" t="n">
         <v>8.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="R3" t="n">
         <v>1.32</v>
@@ -1153,16 +1153,16 @@
         <v>3.35</v>
       </c>
       <c r="T3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="V3" t="n">
         <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="X3" t="n">
         <v>18.5</v>
@@ -1273,10 +1273,10 @@
         <v>5.3</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1291,7 +1291,7 @@
         <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO3" t="n">
         <v>3.15</v>
@@ -1309,7 +1309,7 @@
         <v>18</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU3" t="n">
         <v>7.8</v>
@@ -1324,7 +1324,7 @@
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 12:11:53</t>
+          <t>2026-06-30 14:19:19</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>2.14</v>
       </c>
       <c r="H4" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="O4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1</v>
+        <v>2.34</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.18</v>
+        <v>1.61</v>
       </c>
       <c r="R4" t="n">
-        <v>1.07</v>
+        <v>1.57</v>
       </c>
       <c r="S4" t="n">
-        <v>1.19</v>
+        <v>2.52</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.87</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 12:11:53</t>
+          <t>2026-06-30 14:19:19</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 12:11:53</t>
+          <t>2026-06-30 14:19:19</t>
         </is>
       </c>
     </row>
@@ -1876,55 +1876,55 @@
         <v>2.56</v>
       </c>
       <c r="G6" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="H6" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="I6" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J6" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="U6" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="V6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X6" t="n">
         <v>14</v>
@@ -1942,22 +1942,22 @@
         <v>12</v>
       </c>
       <c r="AC6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF6" t="n">
         <v>22</v>
       </c>
       <c r="AG6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
         <v>55</v>
@@ -1978,7 +1978,7 @@
         <v>36</v>
       </c>
       <c r="AO6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP6" t="n">
         <v>9.199999999999999</v>
@@ -1990,10 +1990,10 @@
         <v>15</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AT6" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU6" t="n">
         <v>6.4</v>
@@ -2002,7 +2002,7 @@
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX6" t="n">
         <v>14.5</v>
@@ -2011,40 +2011,40 @@
         <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="BJ6" t="n">
         <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2056,47 +2056,47 @@
         <v>6.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP6" t="n">
         <v>24</v>
       </c>
       <c r="BQ6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BR6" t="n">
         <v>40</v>
       </c>
       <c r="BS6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU6" t="n">
         <v>4.4</v>
       </c>
       <c r="BV6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BX6" t="n">
         <v>40</v>
       </c>
       <c r="BY6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BZ6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CA6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-30 12:11:53</t>
+          <t>2026-06-30 14:19:19</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-30 12:11:53</t>
+          <t>2026-06-30 14:19:19</t>
         </is>
       </c>
     </row>
@@ -2414,13 +2414,13 @@
         <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R8" t="n">
         <v>1.34</v>
       </c>
       <c r="S8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T8" t="n">
         <v>2.08</v>
@@ -2432,25 +2432,25 @@
         <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="X8" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z8" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AA8" t="n">
         <v>340</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD8" t="n">
         <v>38</v>
@@ -2462,10 +2462,10 @@
         <v>10.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI8" t="n">
         <v>160</v>
@@ -2474,7 +2474,7 @@
         <v>16.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL8" t="n">
         <v>55</v>
@@ -2489,28 +2489,28 @@
         <v>260</v>
       </c>
       <c r="AP8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ8" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW8" t="n">
         <v>4.2</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.5</v>
       </c>
       <c r="AX8" t="n">
         <v>7.4</v>
@@ -2519,28 +2519,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD8" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BF8" t="n">
         <v>7.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BH8" t="n">
         <v>3.5</v>
@@ -2570,7 +2570,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
@@ -2600,11 +2600,11 @@
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>8.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-30 12:11:53</t>
+          <t>2026-06-30 14:19:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G2" t="n">
         <v>2.32</v>
@@ -866,46 +866,46 @@
         <v>3.4</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
         <v>1.38</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="R2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.35</v>
       </c>
       <c r="W2" t="n">
         <v>1.75</v>
@@ -917,10 +917,10 @@
         <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB2" t="n">
         <v>970</v>
@@ -944,7 +944,7 @@
         <v>970</v>
       </c>
       <c r="AI2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ2" t="n">
         <v>34</v>
@@ -953,58 +953,58 @@
         <v>28</v>
       </c>
       <c r="AL2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN2" t="n">
         <v>970</v>
       </c>
       <c r="AO2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AR2" t="n">
         <v>4.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AV2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA2" t="n">
         <v>4.7</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>4.8</v>
       </c>
       <c r="BB2" t="n">
         <v>4.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BD2" t="n">
         <v>4.6</v>
@@ -1013,7 +1013,7 @@
         <v>4.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BG2" t="n">
         <v>4.6</v>
@@ -1028,7 +1028,7 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1037,10 +1037,10 @@
         <v>7.2</v>
       </c>
       <c r="BN2" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BO2" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 14:19:19</t>
+          <t>2026-06-30 16:26:37</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="G3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="H3" t="n">
         <v>6.8</v>
@@ -1126,7 +1126,7 @@
         <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.35</v>
@@ -1135,7 +1135,7 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
         <v>1.3</v>
@@ -1144,43 +1144,43 @@
         <v>1.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
         <v>3.35</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V3" t="n">
         <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="X3" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA3" t="n">
         <v>280</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD3" t="n">
         <v>34</v>
@@ -1198,7 +1198,7 @@
         <v>34</v>
       </c>
       <c r="AI3" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AJ3" t="n">
         <v>16</v>
@@ -1207,10 +1207,10 @@
         <v>23</v>
       </c>
       <c r="AL3" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN3" t="n">
         <v>11.5</v>
@@ -1219,58 +1219,58 @@
         <v>220</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.25</v>
+        <v>5.7</v>
       </c>
       <c r="AU3" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.7</v>
+        <v>19.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.7</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.4</v>
+        <v>13.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BF3" t="n">
         <v>7.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BH3" t="n">
         <v>3.85</v>
@@ -1279,7 +1279,7 @@
         <v>2.9</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK3" t="n">
         <v>8</v>
@@ -1297,7 +1297,7 @@
         <v>3.15</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ3" t="n">
         <v>7</v>
@@ -1318,7 +1318,7 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 14:19:19</t>
+          <t>2026-06-30 16:26:37</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
@@ -1398,139 +1398,139 @@
         <v>2.34</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T4" t="n">
         <v>1.57</v>
       </c>
-      <c r="S4" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.59</v>
-      </c>
       <c r="U4" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="X4" t="n">
         <v>27</v>
       </c>
       <c r="Y4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z4" t="n">
         <v>36</v>
       </c>
       <c r="AA4" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC4" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AE4" t="n">
         <v>46</v>
       </c>
       <c r="AF4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AG4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN4" t="n">
         <v>13</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>10.5</v>
       </c>
       <c r="AO4" t="n">
         <v>36</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.3</v>
+        <v>18</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AT4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW4" t="n">
         <v>4.6</v>
       </c>
-      <c r="AU4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AX4" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.3</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.9</v>
+        <v>16.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.1</v>
+        <v>7.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH4" t="n">
         <v>4.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.199999999999999</v>
@@ -1545,16 +1545,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO4" t="n">
         <v>4.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="BR4" t="n">
         <v>24</v>
@@ -1563,7 +1563,7 @@
         <v>7</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU4" t="n">
         <v>4.3</v>
@@ -1572,13 +1572,13 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ4" t="n">
         <v>17.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 14:19:19</t>
+          <t>2026-06-30 16:26:37</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="H5" t="n">
-        <v>1.02</v>
+        <v>2.8</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 14:19:19</t>
+          <t>2026-06-30 16:26:37</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G6" t="n">
         <v>2.92</v>
@@ -1897,25 +1897,25 @@
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O6" t="n">
         <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R6" t="n">
         <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T6" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
         <v>2.06</v>
@@ -1927,22 +1927,22 @@
         <v>1.52</v>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA6" t="n">
         <v>55</v>
       </c>
       <c r="AB6" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
         <v>15</v>
@@ -1951,7 +1951,7 @@
         <v>40</v>
       </c>
       <c r="AF6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG6" t="n">
         <v>15</v>
@@ -1966,7 +1966,7 @@
         <v>55</v>
       </c>
       <c r="AK6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL6" t="n">
         <v>55</v>
@@ -1981,55 +1981,55 @@
         <v>36</v>
       </c>
       <c r="AP6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT6" t="n">
         <v>9</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AU6" t="n">
         <v>6.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AX6" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AZ6" t="n">
         <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.1</v>
+        <v>20</v>
       </c>
       <c r="BG6" t="n">
         <v>5.2</v>
@@ -2038,7 +2038,7 @@
         <v>3.5</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ6" t="n">
         <v>10.5</v>
@@ -2065,13 +2065,13 @@
         <v>15.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS6" t="n">
         <v>25</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU6" t="n">
         <v>4.4</v>
@@ -2083,20 +2083,20 @@
         <v>16</v>
       </c>
       <c r="BX6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY6" t="n">
         <v>25</v>
       </c>
       <c r="BZ6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA6" t="n">
         <v>21</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-30 14:19:19</t>
+          <t>2026-06-30 16:26:37</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-30 14:19:19</t>
+          <t>2026-06-30 16:26:37</t>
         </is>
       </c>
     </row>
@@ -2384,13 +2384,13 @@
         <v>1.49</v>
       </c>
       <c r="G8" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J8" t="n">
         <v>4.2</v>
@@ -2438,79 +2438,79 @@
         <v>18.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="Z8" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AA8" t="n">
         <v>340</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AE8" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG8" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG8" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AH8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI8" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ8" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AK8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM8" t="n">
         <v>210</v>
       </c>
       <c r="AN8" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO8" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AP8" t="n">
         <v>13</v>
       </c>
       <c r="AQ8" t="n">
-        <v>20</v>
+        <v>7.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.9</v>
+        <v>26</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="AX8" t="n">
         <v>7.4</v>
@@ -2519,28 +2519,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.95</v>
+        <v>7.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.2</v>
+        <v>9.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC8" t="n">
         <v>15</v>
       </c>
       <c r="BD8" t="n">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="BF8" t="n">
         <v>7.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="BH8" t="n">
         <v>3.5</v>
@@ -2564,13 +2564,13 @@
         <v>3.9</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BP8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
@@ -2582,7 +2582,7 @@
         <v>11.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
@@ -2600,11 +2600,11 @@
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-30 14:19:19</t>
+          <t>2026-06-30 16:26:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -860,7 +860,7 @@
         <v>2.14</v>
       </c>
       <c r="G2" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H2" t="n">
         <v>3.4</v>
@@ -869,10 +869,10 @@
         <v>3.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
         <v>1.38</v>
@@ -881,142 +881,142 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O2" t="n">
         <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="T2" t="n">
         <v>1.72</v>
       </c>
       <c r="U2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V2" t="n">
         <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X2" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z2" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AA2" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AC2" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD2" t="n">
         <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AF2" t="n">
         <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH2" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AI2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN2" t="n">
         <v>55</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>970</v>
-      </c>
       <c r="AO2" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="AQ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS2" t="n">
         <v>4</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AT2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA2" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BB2" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BF2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH2" t="n">
         <v>3.6</v>
@@ -1028,7 +1028,7 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1040,13 +1040,13 @@
         <v>18</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 16:26:37</t>
+          <t>2026-06-30 18:33:41</t>
         </is>
       </c>
     </row>
@@ -1111,67 +1111,67 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G3" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="H3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
         <v>3.35</v>
       </c>
       <c r="T3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W3" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="X3" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="Y3" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="Z3" t="n">
-        <v>80</v>
+        <v>270</v>
       </c>
       <c r="AA3" t="n">
         <v>280</v>
@@ -1180,103 +1180,103 @@
         <v>8</v>
       </c>
       <c r="AC3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AE3" t="n">
-        <v>170</v>
+        <v>480</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.4</v>
+        <v>17</v>
       </c>
       <c r="AG3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AI3" t="n">
-        <v>150</v>
+        <v>390</v>
       </c>
       <c r="AJ3" t="n">
-        <v>16</v>
+        <v>180</v>
       </c>
       <c r="AK3" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>200</v>
+        <v>390</v>
       </c>
       <c r="AN3" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AO3" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AP3" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.3</v>
+        <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AU3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX3" t="n">
         <v>7.4</v>
       </c>
-      <c r="AV3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AY3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB3" t="n">
         <v>9.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>13.5</v>
+        <v>6.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.8</v>
+        <v>15</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="BJ3" t="n">
         <v>12</v>
@@ -1294,25 +1294,25 @@
         <v>4.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BP3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BT3" t="n">
         <v>11.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
@@ -1324,7 +1324,7 @@
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 16:26:37</t>
+          <t>2026-06-30 18:33:41</t>
         </is>
       </c>
     </row>
@@ -1371,16 +1371,16 @@
         <v>2.18</v>
       </c>
       <c r="H4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J4" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
         <v>1.25</v>
@@ -1401,7 +1401,7 @@
         <v>1.62</v>
       </c>
       <c r="R4" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S4" t="n">
         <v>2.54</v>
@@ -1425,10 +1425,10 @@
         <v>22</v>
       </c>
       <c r="Z4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA4" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AB4" t="n">
         <v>16</v>
@@ -1437,19 +1437,19 @@
         <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AI4" t="n">
         <v>48</v>
@@ -1458,16 +1458,16 @@
         <v>32</v>
       </c>
       <c r="AK4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM4" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AO4" t="n">
         <v>36</v>
@@ -1479,10 +1479,10 @@
         <v>15</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT4" t="n">
         <v>9.6</v>
@@ -1494,7 +1494,7 @@
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="AX4" t="n">
         <v>11</v>
@@ -1506,7 +1506,7 @@
         <v>11</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BB4" t="n">
         <v>21</v>
@@ -1515,16 +1515,16 @@
         <v>16.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF4" t="n">
         <v>7.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH4" t="n">
         <v>4.4</v>
@@ -1548,7 +1548,7 @@
         <v>5.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="BP4" t="n">
         <v>14</v>
@@ -1566,7 +1566,7 @@
         <v>7.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 16:26:37</t>
+          <t>2026-06-30 18:33:41</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Q5" t="n">
         <v>1.26</v>
       </c>
-      <c r="G5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.05</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.08</v>
+        <v>2.14</v>
       </c>
       <c r="S5" t="n">
-        <v>1.05</v>
+        <v>1.64</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 16:26:37</t>
+          <t>2026-06-30 18:33:41</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="G6" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
         <v>1.4</v>
@@ -1897,28 +1897,28 @@
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O6" t="n">
         <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
         <v>3.35</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V6" t="n">
         <v>1.5</v>
@@ -1927,16 +1927,16 @@
         <v>1.52</v>
       </c>
       <c r="X6" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y6" t="n">
         <v>13.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AB6" t="n">
         <v>13.5</v>
@@ -1945,64 +1945,64 @@
         <v>8.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AF6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG6" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH6" t="n">
         <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AJ6" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AK6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL6" t="n">
         <v>55</v>
       </c>
       <c r="AM6" t="n">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO6" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AP6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="AT6" t="n">
         <v>9</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="AX6" t="n">
         <v>13.5</v>
@@ -2014,34 +2014,34 @@
         <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF6" t="n">
         <v>20</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH6" t="n">
         <v>3.5</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK6" t="n">
         <v>7</v>
@@ -2059,7 +2059,7 @@
         <v>4.4</v>
       </c>
       <c r="BP6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ6" t="n">
         <v>15.5</v>
@@ -2071,32 +2071,32 @@
         <v>25</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU6" t="n">
         <v>4.4</v>
       </c>
       <c r="BV6" t="n">
+        <v>23</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>36</v>
+      </c>
+      <c r="BY6" t="n">
         <v>24</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>38</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>25</v>
       </c>
       <c r="BZ6" t="n">
         <v>32</v>
       </c>
       <c r="CA6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-30 16:26:37</t>
+          <t>2026-06-30 18:33:41</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-30 16:26:37</t>
+          <t>2026-06-30 18:33:41</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
         <v>4.2</v>
       </c>
       <c r="K8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L8" t="n">
         <v>1.4</v>
@@ -2405,46 +2405,46 @@
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O8" t="n">
         <v>1.32</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
         <v>1.94</v>
       </c>
       <c r="R8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T8" t="n">
         <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V8" t="n">
         <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="X8" t="n">
         <v>18.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="Z8" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AA8" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
         <v>7.6</v>
@@ -2453,7 +2453,7 @@
         <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AE8" t="n">
         <v>170</v>
@@ -2465,7 +2465,7 @@
         <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI8" t="n">
         <v>150</v>
@@ -2474,10 +2474,10 @@
         <v>14</v>
       </c>
       <c r="AK8" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AL8" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
         <v>210</v>
@@ -2495,10 +2495,10 @@
         <v>7.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT8" t="n">
         <v>6.6</v>
@@ -2507,10 +2507,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV8" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX8" t="n">
         <v>7.4</v>
@@ -2519,28 +2519,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>7.4</v>
+        <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BF8" t="n">
         <v>7.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BH8" t="n">
         <v>3.5</v>
@@ -2570,7 +2570,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-30 16:26:37</t>
+          <t>2026-06-30 18:33:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -857,58 +857,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="H2" t="n">
         <v>3.4</v>
       </c>
       <c r="I2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K2" t="n">
         <v>3.8</v>
       </c>
-      <c r="J2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.9</v>
-      </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="T2" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U2" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="V2" t="n">
         <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="X2" t="n">
         <v>500</v>
@@ -923,7 +923,7 @@
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="AC2" t="n">
         <v>14</v>
@@ -974,7 +974,7 @@
         <v>11.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="AT2" t="n">
         <v>5.6</v>
@@ -986,7 +986,7 @@
         <v>8.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.5</v>
+        <v>3.85</v>
       </c>
       <c r="AX2" t="n">
         <v>7.6</v>
@@ -995,22 +995,22 @@
         <v>6.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.3</v>
+        <v>3.75</v>
       </c>
       <c r="BE2" t="n">
-        <v>4</v>
+        <v>2.98</v>
       </c>
       <c r="BF2" t="n">
         <v>5</v>
@@ -1019,25 +1019,25 @@
         <v>7.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>7.2</v>
+        <v>1.88</v>
       </c>
       <c r="BN2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BO2" t="n">
         <v>4.1</v>
@@ -1046,13 +1046,13 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
@@ -1064,13 +1064,13 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.85</v>
+        <v>8</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 18:33:41</t>
+          <t>2026-06-30 20:40:51</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G3" t="n">
         <v>1.49</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="I3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K3" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.34</v>
@@ -1159,7 +1159,7 @@
         <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
         <v>3</v>
@@ -1192,7 +1192,7 @@
         <v>17</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH3" t="n">
         <v>75</v>
@@ -1228,7 +1228,7 @@
         <v>8</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT3" t="n">
         <v>6.2</v>
@@ -1240,7 +1240,7 @@
         <v>6.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX3" t="n">
         <v>7.4</v>
@@ -1249,7 +1249,7 @@
         <v>8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BA3" t="n">
         <v>8.4</v>
@@ -1258,13 +1258,13 @@
         <v>9.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD3" t="n">
         <v>7.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF3" t="n">
         <v>7.2</v>
@@ -1279,7 +1279,7 @@
         <v>2.98</v>
       </c>
       <c r="BJ3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK3" t="n">
         <v>8</v>
@@ -1306,7 +1306,7 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BT3" t="n">
         <v>11.5</v>
@@ -1324,7 +1324,7 @@
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 18:33:41</t>
+          <t>2026-06-30 20:40:51</t>
         </is>
       </c>
     </row>
@@ -1368,13 +1368,13 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H4" t="n">
         <v>3.4</v>
       </c>
       <c r="I4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
         <v>3.75</v>
@@ -1383,7 +1383,7 @@
         <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
@@ -1401,7 +1401,7 @@
         <v>1.62</v>
       </c>
       <c r="R4" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="S4" t="n">
         <v>2.54</v>
@@ -1416,7 +1416,7 @@
         <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X4" t="n">
         <v>27</v>
@@ -1506,7 +1506,7 @@
         <v>11</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BB4" t="n">
         <v>21</v>
@@ -1524,7 +1524,7 @@
         <v>7.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BH4" t="n">
         <v>4.4</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 18:33:41</t>
+          <t>2026-06-30 20:40:51</t>
         </is>
       </c>
     </row>
@@ -1619,67 +1619,67 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="G5" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="J5" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="K5" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.02</v>
+        <v>1.83</v>
       </c>
       <c r="O5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P5" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="R5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="S5" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="T5" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="U5" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="V5" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="X5" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="Y5" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="Z5" t="n">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
@@ -1688,22 +1688,22 @@
         <v>55</v>
       </c>
       <c r="AC5" t="n">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AD5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>200</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG5" t="n">
         <v>36</v>
       </c>
-      <c r="AE5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
         <v>150</v>
@@ -1712,22 +1712,22 @@
         <v>180</v>
       </c>
       <c r="AK5" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
         <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AN5" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="AO5" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.55</v>
+        <v>2.38</v>
       </c>
       <c r="AQ5" t="n">
         <v>4.2</v>
@@ -1739,10 +1739,10 @@
         <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.8</v>
+        <v>2.34</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.6</v>
+        <v>2.24</v>
       </c>
       <c r="AV5" t="n">
         <v>4.2</v>
@@ -1751,31 +1751,31 @@
         <v>4.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.6</v>
+        <v>2.42</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.8</v>
+        <v>2.34</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.5</v>
+        <v>2.28</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.3</v>
+        <v>2.24</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.2</v>
+        <v>2.38</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="BG5" t="n">
         <v>6.4</v>
@@ -1790,59 +1790,59 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>2.06</v>
+        <v>1.24</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>2.74</v>
+        <v>1.82</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 18:33:41</t>
+          <t>2026-06-30 20:40:51</t>
         </is>
       </c>
     </row>
@@ -1876,13 +1876,13 @@
         <v>2.6</v>
       </c>
       <c r="G6" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H6" t="n">
         <v>2.64</v>
       </c>
       <c r="I6" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J6" t="n">
         <v>3.2</v>
@@ -1921,7 +1921,7 @@
         <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W6" t="n">
         <v>1.52</v>
@@ -1990,7 +1990,7 @@
         <v>15.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AT6" t="n">
         <v>9</v>
@@ -2014,25 +2014,25 @@
         <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BC6" t="n">
         <v>14.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BF6" t="n">
         <v>20</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH6" t="n">
         <v>3.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-30 18:33:41</t>
+          <t>2026-06-30 20:40:51</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-30 18:33:41</t>
+          <t>2026-06-30 20:40:51</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H8" t="n">
         <v>7.6</v>
@@ -2393,7 +2393,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
         <v>4.7</v>
@@ -2405,13 +2405,13 @@
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
         <v>1.32</v>
       </c>
       <c r="P8" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q8" t="n">
         <v>1.94</v>
@@ -2426,10 +2426,10 @@
         <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V8" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W8" t="n">
         <v>2.78</v>
@@ -2471,7 +2471,7 @@
         <v>150</v>
       </c>
       <c r="AJ8" t="n">
-        <v>14</v>
+        <v>180</v>
       </c>
       <c r="AK8" t="n">
         <v>29</v>
@@ -2492,13 +2492,13 @@
         <v>13</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT8" t="n">
         <v>6.6</v>
@@ -2510,7 +2510,7 @@
         <v>22</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX8" t="n">
         <v>7.4</v>
@@ -2522,25 +2522,25 @@
         <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB8" t="n">
         <v>11.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>12.5</v>
+        <v>6.6</v>
       </c>
       <c r="BD8" t="n">
         <v>30</v>
       </c>
       <c r="BE8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF8" t="n">
         <v>7.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH8" t="n">
         <v>3.5</v>
@@ -2564,13 +2564,13 @@
         <v>3.9</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="BP8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
@@ -2582,7 +2582,7 @@
         <v>11.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-30 18:33:41</t>
+          <t>2026-06-30 20:40:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -884,25 +884,25 @@
         <v>3.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P2" t="n">
         <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S2" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V2" t="n">
         <v>1.36</v>
@@ -914,7 +914,7 @@
         <v>500</v>
       </c>
       <c r="Y2" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
         <v>500</v>
@@ -971,10 +971,10 @@
         <v>7</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.05</v>
+        <v>2.56</v>
       </c>
       <c r="AT2" t="n">
         <v>5.6</v>
@@ -986,7 +986,7 @@
         <v>8.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="AX2" t="n">
         <v>7.6</v>
@@ -998,19 +998,19 @@
         <v>6.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="BF2" t="n">
         <v>5</v>
@@ -1022,37 +1022,37 @@
         <v>3.45</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="BN2" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>12.5</v>
+        <v>6.6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
@@ -1064,13 +1064,13 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>8</v>
+        <v>1.34</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 20:40:51</t>
+          <t>2026-06-30 22:48:17</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G3" t="n">
         <v>1.49</v>
@@ -1141,22 +1141,22 @@
         <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
         <v>3.35</v>
       </c>
       <c r="T3" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V3" t="n">
         <v>1.13</v>
@@ -1189,7 +1189,7 @@
         <v>480</v>
       </c>
       <c r="AF3" t="n">
-        <v>17</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG3" t="n">
         <v>10</v>
@@ -1225,10 +1225,10 @@
         <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT3" t="n">
         <v>6.2</v>
@@ -1237,7 +1237,7 @@
         <v>8.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AW3" t="n">
         <v>8.6</v>
@@ -1249,10 +1249,10 @@
         <v>8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB3" t="n">
         <v>9.6</v>
@@ -1261,28 +1261,28 @@
         <v>6.4</v>
       </c>
       <c r="BD3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF3" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>7.2</v>
       </c>
       <c r="BG3" t="n">
         <v>15</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1309,7 +1309,7 @@
         <v>18</v>
       </c>
       <c r="BT3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BU3" t="n">
         <v>8</v>
@@ -1318,7 +1318,7 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 20:40:51</t>
+          <t>2026-06-30 22:48:17</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="G4" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
         <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
@@ -1395,7 +1395,7 @@
         <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q4" t="n">
         <v>1.62</v>
@@ -1404,31 +1404,31 @@
         <v>1.54</v>
       </c>
       <c r="S4" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="T4" t="n">
         <v>1.57</v>
       </c>
       <c r="U4" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="X4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="Y4" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AA4" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AB4" t="n">
         <v>16</v>
@@ -1437,10 +1437,10 @@
         <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AF4" t="n">
         <v>16.5</v>
@@ -1449,10 +1449,10 @@
         <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI4" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AJ4" t="n">
         <v>32</v>
@@ -1470,7 +1470,7 @@
         <v>11.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AP4" t="n">
         <v>18</v>
@@ -1482,7 +1482,7 @@
         <v>10.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AT4" t="n">
         <v>9.6</v>
@@ -1506,7 +1506,7 @@
         <v>11</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
         <v>21</v>
@@ -1518,16 +1518,16 @@
         <v>16</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF4" t="n">
         <v>7.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI4" t="n">
         <v>3.25</v>
@@ -1536,34 +1536,34 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN4" t="n">
         <v>5.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP4" t="n">
         <v>14</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BR4" t="n">
         <v>24</v>
       </c>
       <c r="BS4" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU4" t="n">
         <v>5.5</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ4" t="n">
         <v>17.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 20:40:51</t>
+          <t>2026-06-30 22:48:17</t>
         </is>
       </c>
     </row>
@@ -1622,22 +1622,22 @@
         <v>1.4</v>
       </c>
       <c r="G5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I5" t="n">
         <v>7.4</v>
       </c>
       <c r="J5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
@@ -1649,28 +1649,28 @@
         <v>1.09</v>
       </c>
       <c r="P5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="R5" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="S5" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="T5" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="U5" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="V5" t="n">
         <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X5" t="n">
         <v>120</v>
@@ -1721,13 +1721,13 @@
         <v>60</v>
       </c>
       <c r="AN5" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="AO5" t="n">
         <v>44</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>4.2</v>
@@ -1739,10 +1739,10 @@
         <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="AV5" t="n">
         <v>4.2</v>
@@ -1751,31 +1751,31 @@
         <v>4.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="AY5" t="n">
-        <v>4</v>
+        <v>2.48</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="BA5" t="n">
         <v>4.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.24</v>
+        <v>2.46</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.38</v>
+        <v>2.68</v>
       </c>
       <c r="BE5" t="n">
         <v>2.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BG5" t="n">
         <v>6.4</v>
@@ -1784,65 +1784,65 @@
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 20:40:51</t>
+          <t>2026-06-30 22:48:17</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>2.6</v>
       </c>
       <c r="G6" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H6" t="n">
         <v>2.64</v>
@@ -1906,7 +1906,7 @@
         <v>1.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
         <v>1.32</v>
@@ -2023,10 +2023,10 @@
         <v>14.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF6" t="n">
         <v>20</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-30 20:40:51</t>
+          <t>2026-06-30 22:48:17</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-30 20:40:51</t>
+          <t>2026-06-30 22:48:17</t>
         </is>
       </c>
     </row>
@@ -2384,55 +2384,55 @@
         <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="H8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K8" t="n">
         <v>4.7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O8" t="n">
         <v>1.32</v>
       </c>
       <c r="P8" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R8" t="n">
         <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T8" t="n">
         <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V8" t="n">
         <v>1.13</v>
       </c>
       <c r="W8" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="X8" t="n">
         <v>18.5</v>
@@ -2441,25 +2441,25 @@
         <v>40</v>
       </c>
       <c r="Z8" t="n">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="AA8" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AB8" t="n">
         <v>7.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD8" t="n">
         <v>75</v>
       </c>
       <c r="AE8" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG8" t="n">
         <v>10.5</v>
@@ -2471,7 +2471,7 @@
         <v>150</v>
       </c>
       <c r="AJ8" t="n">
-        <v>180</v>
+        <v>14</v>
       </c>
       <c r="AK8" t="n">
         <v>29</v>
@@ -2480,25 +2480,25 @@
         <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AO8" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AP8" t="n">
         <v>13</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT8" t="n">
         <v>6.6</v>
@@ -2510,7 +2510,7 @@
         <v>22</v>
       </c>
       <c r="AW8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX8" t="n">
         <v>7.4</v>
@@ -2522,89 +2522,89 @@
         <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB8" t="n">
         <v>11.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BD8" t="n">
         <v>30</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH8" t="n">
         <v>3.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN8" t="n">
         <v>3.9</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BP8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-30 20:40:51</t>
+          <t>2026-06-30 22:48:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -857,100 +857,100 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="G2" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I2" t="n">
         <v>3.85</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S2" t="n">
         <v>3.6</v>
       </c>
-      <c r="O2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.35</v>
       </c>
-      <c r="S2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.36</v>
-      </c>
       <c r="W2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X2" t="n">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AA2" t="n">
-        <v>900</v>
+        <v>440</v>
       </c>
       <c r="AB2" t="n">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>14</v>
+        <v>9.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AF2" t="n">
-        <v>970</v>
+        <v>28</v>
       </c>
       <c r="AG2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>36</v>
       </c>
-      <c r="AH2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>900</v>
-      </c>
       <c r="AK2" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AL2" t="n">
         <v>500</v>
@@ -962,67 +962,67 @@
         <v>55</v>
       </c>
       <c r="AO2" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.56</v>
+        <v>46</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY2" t="n">
         <v>8.4</v>
       </c>
-      <c r="AW2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.9</v>
+        <v>34</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="BC2" t="n">
-        <v>7</v>
+        <v>17.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.3</v>
+        <v>9.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.2</v>
+        <v>26</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
@@ -1034,25 +1034,25 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.87</v>
+        <v>4</v>
       </c>
       <c r="BN2" t="n">
-        <v>18.5</v>
+        <v>5.3</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.34</v>
+        <v>1.76</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
@@ -1064,13 +1064,13 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.34</v>
+        <v>1.76</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.36</v>
+        <v>1.78</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 22:48:17</t>
+          <t>2026-07-01 00:55:49</t>
         </is>
       </c>
     </row>
@@ -1117,25 +1117,25 @@
         <v>1.49</v>
       </c>
       <c r="H3" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O3" t="n">
         <v>1.29</v>
@@ -1153,19 +1153,19 @@
         <v>3.35</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="W3" t="n">
         <v>3</v>
       </c>
       <c r="X3" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="Y3" t="n">
         <v>48</v>
@@ -1174,115 +1174,115 @@
         <v>270</v>
       </c>
       <c r="AA3" t="n">
-        <v>280</v>
+        <v>440</v>
       </c>
       <c r="AB3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC3" t="n">
         <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AE3" t="n">
         <v>480</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH3" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AI3" t="n">
-        <v>390</v>
+        <v>190</v>
       </c>
       <c r="AJ3" t="n">
-        <v>180</v>
+        <v>13</v>
       </c>
       <c r="AK3" t="n">
-        <v>65</v>
+        <v>18.5</v>
       </c>
       <c r="AL3" t="n">
         <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>390</v>
+        <v>250</v>
       </c>
       <c r="AN3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU3" t="n">
         <v>9</v>
       </c>
-      <c r="AO3" t="n">
-        <v>210</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ3" t="n">
+      <c r="AV3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE3" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV3" t="n">
+      <c r="BF3" t="n">
         <v>7</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>7.4</v>
       </c>
       <c r="BG3" t="n">
         <v>15</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BJ3" t="n">
         <v>12</v>
       </c>
       <c r="BK3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1291,13 +1291,13 @@
         <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BP3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BQ3" t="n">
         <v>6.8</v>
@@ -1306,25 +1306,25 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BT3" t="n">
         <v>12</v>
       </c>
       <c r="BU3" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 22:48:17</t>
+          <t>2026-07-01 00:55:49</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>2.1</v>
       </c>
       <c r="G4" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="H4" t="n">
         <v>3.35</v>
@@ -1377,7 +1377,7 @@
         <v>3.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K4" t="n">
         <v>4.2</v>
@@ -1416,7 +1416,7 @@
         <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X4" t="n">
         <v>23</v>
@@ -1506,7 +1506,7 @@
         <v>11</v>
       </c>
       <c r="BA4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BB4" t="n">
         <v>21</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 22:48:17</t>
+          <t>2026-07-01 00:55:49</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>1.4</v>
       </c>
       <c r="G5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H5" t="n">
         <v>6.2</v>
@@ -1649,7 +1649,7 @@
         <v>1.09</v>
       </c>
       <c r="P5" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="Q5" t="n">
         <v>1.25</v>
@@ -1670,7 +1670,7 @@
         <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="X5" t="n">
         <v>120</v>
@@ -1724,7 +1724,7 @@
         <v>3.45</v>
       </c>
       <c r="AO5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP5" t="n">
         <v>2.5</v>
@@ -1739,7 +1739,7 @@
         <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="AU5" t="n">
         <v>2.48</v>
@@ -1772,7 +1772,7 @@
         <v>2.68</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BF5" t="n">
         <v>3</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 22:48:17</t>
+          <t>2026-07-01 00:55:49</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         <v>2.92</v>
       </c>
       <c r="H6" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I6" t="n">
         <v>2.96</v>
@@ -1888,7 +1888,7 @@
         <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.4</v>
@@ -1897,19 +1897,19 @@
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q6" t="n">
         <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
         <v>3.35</v>
@@ -1954,10 +1954,10 @@
         <v>21</v>
       </c>
       <c r="AG6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI6" t="n">
         <v>46</v>
@@ -1969,7 +1969,7 @@
         <v>34</v>
       </c>
       <c r="AL6" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
@@ -1990,7 +1990,7 @@
         <v>15.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT6" t="n">
         <v>9</v>
@@ -2014,19 +2014,19 @@
         <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC6" t="n">
         <v>14.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BF6" t="n">
         <v>20</v>
@@ -2038,7 +2038,7 @@
         <v>3.5</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ6" t="n">
         <v>10</v>
@@ -2065,10 +2065,10 @@
         <v>15.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BT6" t="n">
         <v>6.2</v>
@@ -2089,14 +2089,14 @@
         <v>24</v>
       </c>
       <c r="BZ6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="CA6" t="n">
         <v>20</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-30 22:48:17</t>
+          <t>2026-07-01 00:55:49</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-30 22:48:17</t>
+          <t>2026-07-01 00:55:49</t>
         </is>
       </c>
     </row>
@@ -2405,28 +2405,28 @@
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P8" t="n">
         <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S8" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="T8" t="n">
         <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V8" t="n">
         <v>1.13</v>
@@ -2435,7 +2435,7 @@
         <v>2.74</v>
       </c>
       <c r="X8" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y8" t="n">
         <v>40</v>
@@ -2447,7 +2447,7 @@
         <v>320</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC8" t="n">
         <v>10</v>
@@ -2483,7 +2483,7 @@
         <v>200</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AO8" t="n">
         <v>230</v>
@@ -2495,7 +2495,7 @@
         <v>8</v>
       </c>
       <c r="AR8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS8" t="n">
         <v>10.5</v>
@@ -2510,7 +2510,7 @@
         <v>22</v>
       </c>
       <c r="AW8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX8" t="n">
         <v>7.4</v>
@@ -2522,34 +2522,34 @@
         <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB8" t="n">
         <v>11.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="BD8" t="n">
         <v>30</v>
       </c>
       <c r="BE8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="BJ8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK8" t="n">
         <v>6.8</v>
@@ -2558,53 +2558,53 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN8" t="n">
         <v>3.9</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BP8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT8" t="n">
         <v>11</v>
       </c>
       <c r="BU8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-30 22:48:17</t>
+          <t>2026-07-01 00:55:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -857,64 +857,64 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G2" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I2" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
         <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="O2" t="n">
         <v>1.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="U2" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X2" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="Z2" t="n">
         <v>65</v>
@@ -926,10 +926,10 @@
         <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AE2" t="n">
         <v>120</v>
@@ -938,19 +938,19 @@
         <v>28</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
         <v>250</v>
       </c>
       <c r="AJ2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK2" t="n">
         <v>36</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>38</v>
       </c>
       <c r="AL2" t="n">
         <v>500</v>
@@ -959,19 +959,19 @@
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AO2" t="n">
         <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS2" t="n">
         <v>46</v>
@@ -980,97 +980,97 @@
         <v>7.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
         <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AX2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BB2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC2" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD2" t="n">
         <v>17.5</v>
       </c>
-      <c r="BD2" t="n">
-        <v>20</v>
-      </c>
       <c r="BE2" t="n">
-        <v>9.6</v>
+        <v>28</v>
       </c>
       <c r="BF2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="BN2" t="n">
         <v>5.3</v>
       </c>
       <c r="BO2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.76</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.76</v>
+        <v>8</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.78</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>
@@ -1114,112 +1114,112 @@
         <v>1.46</v>
       </c>
       <c r="G3" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="I3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K3" t="n">
         <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="T3" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="V3" t="n">
         <v>1.11</v>
       </c>
       <c r="W3" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="X3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Y3" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="Z3" t="n">
-        <v>270</v>
+        <v>80</v>
       </c>
       <c r="AA3" t="n">
-        <v>440</v>
+        <v>330</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC3" t="n">
         <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE3" t="n">
-        <v>480</v>
+        <v>170</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AI3" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="AJ3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK3" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AM3" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="AN3" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AO3" t="n">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="AP3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>21</v>
@@ -1228,61 +1228,61 @@
         <v>55</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV3" t="n">
         <v>28</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="AX3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY3" t="n">
         <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="BB3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>9.4</v>
+        <v>21</v>
       </c>
       <c r="BE3" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BF3" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BG3" t="n">
         <v>15</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="BJ3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,37 +1294,37 @@
         <v>4.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BP3" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS3" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BT3" t="n">
         <v>12</v>
       </c>
       <c r="BU3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>
@@ -1365,46 +1365,46 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="G4" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J4" t="n">
         <v>3.75</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P4" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R4" t="n">
         <v>1.54</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T4" t="n">
         <v>1.57</v>
@@ -1413,10 +1413,10 @@
         <v>2.44</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="X4" t="n">
         <v>23</v>
@@ -1428,7 +1428,7 @@
         <v>50</v>
       </c>
       <c r="AA4" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AB4" t="n">
         <v>16</v>
@@ -1437,10 +1437,10 @@
         <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
         <v>16.5</v>
@@ -1461,19 +1461,19 @@
         <v>21</v>
       </c>
       <c r="AL4" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="AM4" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="AN4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO4" t="n">
         <v>28</v>
       </c>
       <c r="AP4" t="n">
-        <v>18</v>
+        <v>5.7</v>
       </c>
       <c r="AQ4" t="n">
         <v>15</v>
@@ -1482,113 +1482,113 @@
         <v>10.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AU4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY4" t="n">
         <v>7</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
         <v>11</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>16</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>10</v>
       </c>
       <c r="BN4" t="n">
         <v>5.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BP4" t="n">
         <v>14</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT4" t="n">
         <v>7.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
         <v>17.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="G5" t="n">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="H5" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="I5" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="J5" t="n">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="K5" t="n">
         <v>6.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.83</v>
+        <v>1.02</v>
       </c>
       <c r="O5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P5" t="n">
-        <v>4.1</v>
+        <v>2.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="R5" t="n">
-        <v>2.26</v>
+        <v>1.96</v>
       </c>
       <c r="S5" t="n">
         <v>1.64</v>
       </c>
       <c r="T5" t="n">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="U5" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="W5" t="n">
-        <v>3.1</v>
+        <v>2.26</v>
       </c>
       <c r="X5" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="Y5" t="n">
         <v>130</v>
       </c>
       <c r="Z5" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB5" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AC5" t="n">
         <v>970</v>
       </c>
       <c r="AD5" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="AE5" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="AF5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AR5" t="n">
         <v>40</v>
       </c>
-      <c r="AG5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH5" t="n">
+      <c r="AS5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT5" t="n">
         <v>22</v>
       </c>
-      <c r="AI5" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>180</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN5" t="n">
+      <c r="AU5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY5" t="n">
         <v>3.45</v>
       </c>
-      <c r="AO5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>2.48</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>2.54</v>
+        <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.2</v>
+        <v>26</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.46</v>
+        <v>17.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.46</v>
+        <v>4.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.68</v>
+        <v>7.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.54</v>
+        <v>29</v>
       </c>
       <c r="BF5" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.35</v>
+        <v>2.66</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.42</v>
+        <v>5</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.74</v>
+        <v>4.3</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.35</v>
+        <v>5.9</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.33</v>
+        <v>5.8</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>
@@ -1873,55 +1873,55 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="G6" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H6" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I6" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P6" t="n">
         <v>1.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R6" t="n">
         <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V6" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W6" t="n">
         <v>1.52</v>
@@ -1930,46 +1930,46 @@
         <v>15</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
         <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AB6" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
         <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF6" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG6" t="n">
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ6" t="n">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AK6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
@@ -1990,7 +1990,7 @@
         <v>15.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT6" t="n">
         <v>9</v>
@@ -2014,25 +2014,25 @@
         <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC6" t="n">
         <v>14.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF6" t="n">
         <v>20</v>
       </c>
       <c r="BG6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BH6" t="n">
         <v>3.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>
@@ -2381,61 +2381,61 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="G8" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="H8" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J8" t="n">
         <v>4.2</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P8" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R8" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
         <v>3.55</v>
       </c>
       <c r="T8" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="U8" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="V8" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W8" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="X8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y8" t="n">
         <v>40</v>
@@ -2444,64 +2444,64 @@
         <v>170</v>
       </c>
       <c r="AA8" t="n">
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD8" t="n">
         <v>75</v>
       </c>
       <c r="AE8" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF8" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
         <v>32</v>
       </c>
       <c r="AI8" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ8" t="n">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="AK8" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="AL8" t="n">
         <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="AN8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>9.4</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>230</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>8</v>
       </c>
       <c r="AR8" t="n">
         <v>10.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU8" t="n">
         <v>8.800000000000001</v>
@@ -2510,7 +2510,7 @@
         <v>22</v>
       </c>
       <c r="AW8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX8" t="n">
         <v>7.4</v>
@@ -2522,7 +2522,7 @@
         <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB8" t="n">
         <v>11.5</v>
@@ -2531,46 +2531,46 @@
         <v>12.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>30</v>
+        <v>9.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG8" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN8" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP8" t="n">
         <v>10</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
@@ -2582,7 +2582,7 @@
         <v>11</v>
       </c>
       <c r="BU8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,187 +857,187 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G2" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="H2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K2" t="n">
         <v>3.6</v>
       </c>
-      <c r="I2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L2" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="T2" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="U2" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="X2" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="AA2" t="n">
-        <v>440</v>
+        <v>250</v>
       </c>
       <c r="AB2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC2" t="n">
         <v>9</v>
       </c>
       <c r="AD2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI2" t="n">
         <v>120</v>
       </c>
-      <c r="AF2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH2" t="n">
+      <c r="AJ2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN2" t="n">
         <v>22</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>250</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>36</v>
       </c>
       <c r="AO2" t="n">
         <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AR2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS2" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
         <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD2" t="n">
         <v>17.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>28</v>
+        <v>9.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO2" t="n">
         <v>4.1</v>
@@ -1046,16 +1046,16 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT2" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>7</v>
       </c>
       <c r="BU2" t="n">
         <v>5.2</v>
@@ -1064,13 +1064,13 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>
@@ -1111,178 +1111,178 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="G3" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="H3" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="I3" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K3" t="n">
         <v>4.6</v>
       </c>
-      <c r="K3" t="n">
-        <v>5</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="T3" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="X3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>260</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>480</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>15</v>
       </c>
-      <c r="Y3" t="n">
-        <v>26</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>330</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="AK3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX3" t="n">
         <v>7.4</v>
       </c>
-      <c r="AC3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>270</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AY3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BA3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC3" t="n">
         <v>14.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BE3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BG3" t="n">
         <v>15</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="BJ3" t="n">
         <v>12.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,37 +1294,37 @@
         <v>4.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BP3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BT3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BU3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H4" t="n">
         <v>3.3</v>
       </c>
       <c r="I4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J4" t="n">
         <v>3.75</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
         <v>1.31</v>
@@ -1413,19 +1413,19 @@
         <v>2.44</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
         <v>1.83</v>
       </c>
       <c r="X4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="AA4" t="n">
         <v>160</v>
@@ -1437,7 +1437,7 @@
         <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE4" t="n">
         <v>60</v>
@@ -1458,7 +1458,7 @@
         <v>32</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
         <v>70</v>
@@ -1470,79 +1470,79 @@
         <v>12</v>
       </c>
       <c r="AO4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15</v>
+        <v>7.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT4" t="n">
         <v>11</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="AV4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW4" t="n">
         <v>13</v>
       </c>
-      <c r="AW4" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AX4" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="AY4" t="n">
         <v>7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.8</v>
+        <v>21</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BJ4" t="n">
         <v>9</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BN4" t="n">
         <v>5.4</v>
@@ -1551,16 +1551,16 @@
         <v>4.6</v>
       </c>
       <c r="BP4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BT4" t="n">
         <v>7.4</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K5" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.16</v>
@@ -1643,28 +1643,28 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.02</v>
+        <v>1.97</v>
       </c>
       <c r="O5" t="n">
         <v>1.08</v>
       </c>
       <c r="P5" t="n">
-        <v>2.72</v>
+        <v>3.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="R5" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="S5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="T5" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V5" t="n">
         <v>1.26</v>
@@ -1676,67 +1676,67 @@
         <v>500</v>
       </c>
       <c r="Y5" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="Z5" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AA5" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="AB5" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AC5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF5" t="n">
         <v>970</v>
       </c>
-      <c r="AD5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>28</v>
-      </c>
       <c r="AG5" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
         <v>42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AK5" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AM5" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AN5" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="AO5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.2</v>
+        <v>29</v>
       </c>
       <c r="AQ5" t="n">
         <v>38</v>
       </c>
       <c r="AR5" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="AT5" t="n">
         <v>22</v>
@@ -1745,58 +1745,58 @@
         <v>13.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AW5" t="n">
         <v>32</v>
       </c>
       <c r="AX5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.45</v>
+        <v>5.3</v>
       </c>
       <c r="AZ5" t="n">
         <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB5" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.92</v>
+        <v>3.85</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.4</v>
+        <v>5.7</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
         <v>4</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>2.66</v>
       </c>
       <c r="BN5" t="n">
         <v>6</v>
@@ -1814,7 +1814,7 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
@@ -1826,13 +1826,13 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
         <v>5.9</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>5.8</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="H6" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="I6" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="J6" t="n">
         <v>3.4</v>
@@ -1897,7 +1897,7 @@
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O6" t="n">
         <v>1.33</v>
@@ -1915,13 +1915,13 @@
         <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="U6" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W6" t="n">
         <v>1.52</v>
@@ -1930,19 +1930,19 @@
         <v>15</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z6" t="n">
         <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
         <v>13</v>
@@ -1954,91 +1954,91 @@
         <v>19.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>44</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>120</v>
-      </c>
       <c r="AK6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM6" t="n">
-        <v>580</v>
+        <v>450</v>
       </c>
       <c r="AN6" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AO6" t="n">
         <v>29</v>
       </c>
       <c r="AP6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY6" t="n">
         <v>10</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.8</v>
+        <v>29</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="BC6" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.8</v>
+        <v>29</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG6" t="n">
-        <v>7</v>
+        <v>17.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BJ6" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO6" t="n">
         <v>4.4</v>
@@ -2086,7 +2086,7 @@
         <v>36</v>
       </c>
       <c r="BY6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BZ6" t="n">
         <v>30</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>
@@ -2350,261 +2350,515 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>US USL League One</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Charlotte Independence</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Corpus Christi</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="X8" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>220</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>400</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>320</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-07-01 05:11:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Ecuadorian Serie A</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>LDU</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Orense Sporting Club</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="F9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H9" t="n">
         <v>7</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I9" t="n">
         <v>8</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>4.2</v>
       </c>
-      <c r="K8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O8" t="n">
+      <c r="K9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O9" t="n">
         <v>1.32</v>
       </c>
-      <c r="P8" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="P9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1.98</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="R9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S9" t="n">
         <v>3.55</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>2.02</v>
       </c>
-      <c r="U8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="U9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.14</v>
       </c>
-      <c r="W8" t="n">
+      <c r="W9" t="n">
         <v>2.66</v>
       </c>
-      <c r="X8" t="n">
+      <c r="X9" t="n">
         <v>17</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Y9" t="n">
         <v>40</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="Z9" t="n">
         <v>170</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AA9" t="n">
         <v>280</v>
       </c>
-      <c r="AB8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AE8" t="n">
+      <c r="AB9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE9" t="n">
         <v>150</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AF9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AG9" t="n">
         <v>10</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AH9" t="n">
         <v>32</v>
       </c>
-      <c r="AI8" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK8" t="n">
+      <c r="AI9" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK9" t="n">
         <v>65</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AL9" t="n">
         <v>500</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AM9" t="n">
         <v>700</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AN9" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AO8" t="n">
-        <v>210</v>
-      </c>
-      <c r="AP8" t="n">
+      <c r="AO9" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP9" t="n">
         <v>12.5</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR8" t="n">
+      <c r="AQ9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW9" t="n">
         <v>10.5</v>
       </c>
-      <c r="AS8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU8" t="n">
+      <c r="AX9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AV8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW8" t="n">
+      <c r="AZ9" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB9" t="n">
         <v>11.5</v>
       </c>
-      <c r="AX8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY8" t="n">
+      <c r="BC9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>12</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>15</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>11</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>2026-07-01 03:03:10</t>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,73 +860,73 @@
         <v>2.3</v>
       </c>
       <c r="G2" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H2" t="n">
         <v>3.4</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K2" t="n">
         <v>3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="R2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.39</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.4</v>
       </c>
       <c r="W2" t="n">
         <v>1.72</v>
       </c>
       <c r="X2" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="n">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
         <v>17</v>
@@ -935,19 +935,19 @@
         <v>50</v>
       </c>
       <c r="AF2" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI2" t="n">
         <v>120</v>
       </c>
       <c r="AJ2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK2" t="n">
         <v>34</v>
@@ -956,13 +956,13 @@
         <v>80</v>
       </c>
       <c r="AM2" t="n">
+        <v>380</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO2" t="n">
         <v>500</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>600</v>
       </c>
       <c r="AP2" t="n">
         <v>12</v>
@@ -974,85 +974,85 @@
         <v>19</v>
       </c>
       <c r="AS2" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AX2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BB2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC2" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BD2" t="n">
         <v>17.5</v>
       </c>
       <c r="BE2" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>9.6</v>
       </c>
-      <c r="BF2" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>24</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BK2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN2" t="n">
         <v>5.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT2" t="n">
         <v>6.8</v>
@@ -1064,13 +1064,13 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G3" t="n">
         <v>1.59</v>
@@ -1126,43 +1126,43 @@
         <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V3" t="n">
         <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="X3" t="n">
         <v>14.5</v>
@@ -1183,19 +1183,19 @@
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
         <v>140</v>
@@ -1207,28 +1207,28 @@
         <v>20</v>
       </c>
       <c r="AL3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM3" t="n">
         <v>190</v>
       </c>
       <c r="AN3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP3" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR3" t="n">
         <v>50</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AT3" t="n">
         <v>6.6</v>
@@ -1240,7 +1240,7 @@
         <v>25</v>
       </c>
       <c r="AW3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AX3" t="n">
         <v>7.4</v>
@@ -1252,22 +1252,22 @@
         <v>23</v>
       </c>
       <c r="BA3" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE3" t="n">
         <v>13.5</v>
       </c>
-      <c r="BB3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>14</v>
-      </c>
       <c r="BF3" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG3" t="n">
         <v>15</v>
@@ -1276,13 +1276,13 @@
         <v>3.45</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.64</v>
+        <v>2.9</v>
       </c>
       <c r="BJ3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK3" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1291,28 +1291,28 @@
         <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="BP3" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR3" t="n">
         <v>32</v>
       </c>
       <c r="BS3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BT3" t="n">
         <v>11</v>
       </c>
       <c r="BU3" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G4" t="n">
         <v>2.08</v>
       </c>
-      <c r="G4" t="n">
-        <v>2.2</v>
-      </c>
       <c r="H4" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="R4" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S4" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T4" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="U4" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="X4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Y4" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="Z4" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AA4" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AB4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF4" t="n">
         <v>16</v>
       </c>
-      <c r="AC4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
         <v>16</v>
       </c>
       <c r="AI4" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="AJ4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="AM4" t="n">
         <v>320</v>
       </c>
       <c r="AN4" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.199999999999999</v>
+        <v>19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.6</v>
+        <v>16.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.2</v>
+        <v>25</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.8</v>
+        <v>16</v>
       </c>
       <c r="AT4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE4" t="n">
         <v>11</v>
       </c>
-      <c r="AU4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>7</v>
-      </c>
       <c r="BF4" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH4" t="n">
         <v>4.3</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR4" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>17</v>
+      </c>
+      <c r="CA4" t="n">
         <v>7.4</v>
       </c>
-      <c r="BT4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>18</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>6.8</v>
-      </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -1622,19 +1622,19 @@
         <v>1.6</v>
       </c>
       <c r="G5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J5" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="K5" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.16</v>
@@ -1643,52 +1643,52 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="O5" t="n">
         <v>1.08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="R5" t="n">
         <v>2.16</v>
       </c>
       <c r="S5" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="T5" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="U5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X5" t="n">
         <v>500</v>
       </c>
       <c r="Y5" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z5" t="n">
         <v>70</v>
       </c>
-      <c r="Z5" t="n">
-        <v>75</v>
-      </c>
       <c r="AA5" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB5" t="n">
         <v>500</v>
       </c>
       <c r="AC5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD5" t="n">
         <v>23</v>
@@ -1700,16 +1700,16 @@
         <v>970</v>
       </c>
       <c r="AG5" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI5" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ5" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AK5" t="n">
         <v>15.5</v>
@@ -1718,16 +1718,16 @@
         <v>22</v>
       </c>
       <c r="AM5" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AN5" t="n">
         <v>4.9</v>
       </c>
       <c r="AO5" t="n">
-        <v>23</v>
+        <v>270</v>
       </c>
       <c r="AP5" t="n">
-        <v>29</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ5" t="n">
         <v>38</v>
@@ -1736,73 +1736,73 @@
         <v>29</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AT5" t="n">
         <v>22</v>
       </c>
       <c r="AU5" t="n">
-        <v>13.5</v>
+        <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW5" t="n">
         <v>32</v>
       </c>
       <c r="AX5" t="n">
-        <v>17</v>
+        <v>9.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB5" t="n">
         <v>20</v>
       </c>
       <c r="BC5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE5" t="n">
         <v>34</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BI5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO5" t="n">
         <v>3.55</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>3.3</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
@@ -1835,14 +1835,14 @@
         <v>5.9</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="CA5" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G6" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="H6" t="n">
         <v>2.72</v>
@@ -1891,58 +1891,58 @@
         <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="V6" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="X6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Y6" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Z6" t="n">
         <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AB6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
         <v>13</v>
@@ -1951,58 +1951,58 @@
         <v>32</v>
       </c>
       <c r="AF6" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AG6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI6" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK6" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL6" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM6" t="n">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="AN6" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AO6" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AP6" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV6" t="n">
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX6" t="n">
         <v>16</v>
@@ -2014,37 +2014,37 @@
         <v>14</v>
       </c>
       <c r="BA6" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BB6" t="n">
-        <v>32</v>
+        <v>18.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BG6" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="BJ6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2053,50 +2053,50 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO6" t="n">
         <v>4.4</v>
       </c>
       <c r="BP6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BQ6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BT6" t="n">
         <v>6.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BX6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BZ6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="CA6" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="G8" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="H8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I8" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K8" t="n">
         <v>5.2</v>
@@ -2405,16 +2405,16 @@
         <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O8" t="n">
         <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R8" t="n">
         <v>1.58</v>
@@ -2423,43 +2423,43 @@
         <v>2.48</v>
       </c>
       <c r="T8" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="U8" t="n">
         <v>2.12</v>
       </c>
       <c r="V8" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W8" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="X8" t="n">
         <v>25</v>
       </c>
       <c r="Y8" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="Z8" t="n">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="AA8" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AB8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC8" t="n">
         <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="AE8" t="n">
         <v>400</v>
       </c>
       <c r="AF8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG8" t="n">
         <v>11</v>
@@ -2471,22 +2471,22 @@
         <v>320</v>
       </c>
       <c r="AJ8" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL8" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AO8" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP8" t="n">
         <v>19</v>
@@ -2495,37 +2495,37 @@
         <v>21</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AU8" t="n">
-        <v>9</v>
-      </c>
       <c r="AV8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY8" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC8" t="n">
         <v>13</v>
@@ -2534,13 +2534,13 @@
         <v>18</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -2638,16 +2638,16 @@
         <v>1.53</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K9" t="n">
         <v>4.6</v>
@@ -2659,7 +2659,7 @@
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O9" t="n">
         <v>1.32</v>
@@ -2668,197 +2668,959 @@
         <v>1.96</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
         <v>3.55</v>
       </c>
       <c r="T9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="V9" t="n">
         <v>1.14</v>
       </c>
       <c r="W9" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="X9" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Y9" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="Z9" t="n">
         <v>170</v>
       </c>
       <c r="AA9" t="n">
-        <v>280</v>
+        <v>700</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AD9" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AE9" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AF9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AI9" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AJ9" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AK9" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="AL9" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AM9" t="n">
         <v>700</v>
       </c>
       <c r="AN9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AO9" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AP9" t="n">
-        <v>12.5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV9" t="n">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="AW9" t="n">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="BB9" t="n">
         <v>11.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BE9" t="n">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BI9" t="n">
         <v>2.88</v>
       </c>
       <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-07-01 07:18:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>US USL League One</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Chattanooga Red Wolves SC</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Westchester SC</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="X10" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB10" t="n">
         <v>11.5</v>
       </c>
-      <c r="BK9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
+      <c r="BC10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>60</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>36</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>36</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>11</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-07-01 07:18:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>US USL League One</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>23:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Spokane Velocity FC</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Forward Madison FC</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>36</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>23</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>30</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>21</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-07-01 07:18:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>US USL League One</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>23:30:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Union Omaha</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AV Alta FC</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X12" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>65</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>22</v>
+      </c>
+      <c r="BS12" t="n">
         <v>15</v>
       </c>
-      <c r="BN9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BP9" t="n">
+      <c r="BT12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>32</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>32</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="CA12" t="n">
         <v>10</v>
       </c>
-      <c r="BQ9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>2026-07-01 05:11:03</t>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H2" t="n">
         <v>3.4</v>
@@ -872,55 +872,55 @@
         <v>3.45</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U2" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="V2" t="n">
         <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z2" t="n">
         <v>32</v>
       </c>
       <c r="AA2" t="n">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="AB2" t="n">
         <v>12</v>
@@ -929,148 +929,148 @@
         <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK2" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AL2" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="AM2" t="n">
         <v>380</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS2" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY2" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
         <v>32</v>
       </c>
       <c r="BB2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BC2" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>17.5</v>
+        <v>27</v>
       </c>
       <c r="BE2" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="BF2" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BH2" t="n">
         <v>3.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BN2" t="n">
         <v>5.1</v>
       </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BO2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="BT2" t="n">
         <v>6.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.8</v>
+        <v>3.3</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.4</v>
+        <v>3.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -1111,25 +1111,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="G3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="I3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
         <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
@@ -1138,55 +1138,55 @@
         <v>3.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R3" t="n">
         <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T3" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V3" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W3" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="X3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y3" t="n">
         <v>22</v>
       </c>
       <c r="Z3" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AA3" t="n">
         <v>260</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE3" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="AF3" t="n">
         <v>8.800000000000001</v>
@@ -1195,31 +1195,31 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI3" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ3" t="n">
         <v>15</v>
       </c>
       <c r="AK3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AP3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ3" t="n">
         <v>19</v>
@@ -1228,7 +1228,7 @@
         <v>50</v>
       </c>
       <c r="AS3" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT3" t="n">
         <v>6.6</v>
@@ -1240,31 +1240,31 @@
         <v>25</v>
       </c>
       <c r="AW3" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA3" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BB3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD3" t="n">
         <v>36</v>
       </c>
       <c r="BE3" t="n">
-        <v>13.5</v>
+        <v>95</v>
       </c>
       <c r="BF3" t="n">
         <v>9.199999999999999</v>
@@ -1273,10 +1273,10 @@
         <v>15</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="BJ3" t="n">
         <v>12</v>
@@ -1291,16 +1291,16 @@
         <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BR3" t="n">
         <v>32</v>
@@ -1312,16 +1312,16 @@
         <v>11</v>
       </c>
       <c r="BU3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW3" t="n">
         <v>48</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY3" t="n">
         <v>50</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -1365,85 +1365,85 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="G4" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="H4" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="O4" t="n">
         <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="R4" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="T4" t="n">
         <v>1.63</v>
       </c>
       <c r="U4" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="X4" t="n">
         <v>24</v>
       </c>
       <c r="Y4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Z4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA4" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AB4" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE4" t="n">
         <v>42</v>
       </c>
       <c r="AF4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
@@ -1452,97 +1452,97 @@
         <v>16</v>
       </c>
       <c r="AI4" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AL4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AM4" t="n">
         <v>320</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AO4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP4" t="n">
         <v>19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AS4" t="n">
         <v>16</v>
       </c>
       <c r="AT4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX4" t="n">
         <v>13</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG4" t="n">
         <v>23</v>
       </c>
-      <c r="BE4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>22</v>
-      </c>
       <c r="BH4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BJ4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN4" t="n">
         <v>5.2</v>
@@ -1551,19 +1551,19 @@
         <v>4.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BU4" t="n">
         <v>5</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BZ4" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -1619,166 +1619,166 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="G5" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="I5" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="K5" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.99</v>
+        <v>6.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P5" t="n">
         <v>3.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="R5" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="S5" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="T5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="V5" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="X5" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="Y5" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI5" t="n">
         <v>55</v>
       </c>
-      <c r="Z5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI5" t="n">
+      <c r="AJ5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP5" t="n">
         <v>38</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>270</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AQ5" t="n">
         <v>38</v>
       </c>
       <c r="AR5" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.6</v>
+        <v>75</v>
       </c>
       <c r="AT5" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="AY5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BB5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BC5" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>9.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="BH5" t="n">
         <v>7</v>
@@ -1790,13 +1790,13 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BN5" t="n">
         <v>5.9</v>
@@ -1814,13 +1814,13 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
@@ -1832,17 +1832,17 @@
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BZ5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -1873,25 +1873,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H6" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I6" t="n">
         <v>2.98</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -1903,10 +1903,10 @@
         <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="R6" t="n">
         <v>1.4</v>
@@ -1915,25 +1915,25 @@
         <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U6" t="n">
         <v>2.24</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W6" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y6" t="n">
         <v>13.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA6" t="n">
         <v>44</v>
@@ -1942,7 +1942,7 @@
         <v>13</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
         <v>13</v>
@@ -1951,22 +1951,22 @@
         <v>32</v>
       </c>
       <c r="AF6" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL6" t="n">
         <v>40</v>
@@ -1975,7 +1975,7 @@
         <v>200</v>
       </c>
       <c r="AN6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO6" t="n">
         <v>25</v>
@@ -1984,13 +1984,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS6" t="n">
-        <v>18.5</v>
+        <v>29</v>
       </c>
       <c r="AT6" t="n">
         <v>10.5</v>
@@ -2008,16 +2008,16 @@
         <v>16</v>
       </c>
       <c r="AY6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BB6" t="n">
-        <v>18.5</v>
+        <v>27</v>
       </c>
       <c r="BC6" t="n">
         <v>21</v>
@@ -2026,10 +2026,10 @@
         <v>27</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.8</v>
+        <v>29</v>
       </c>
       <c r="BF6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BG6" t="n">
         <v>19.5</v>
@@ -2038,10 +2038,10 @@
         <v>3.7</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK6" t="n">
         <v>6.8</v>
@@ -2053,7 +2053,7 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO6" t="n">
         <v>4.4</v>
@@ -2065,7 +2065,7 @@
         <v>14.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS6" t="n">
         <v>22</v>
@@ -2080,23 +2080,23 @@
         <v>22</v>
       </c>
       <c r="BW6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BX6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY6" t="n">
         <v>22</v>
       </c>
       <c r="BZ6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CA6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -2387,13 +2387,13 @@
         <v>1.6</v>
       </c>
       <c r="H8" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="I8" t="n">
         <v>7.4</v>
       </c>
       <c r="J8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
         <v>5.2</v>
@@ -2411,7 +2411,7 @@
         <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q8" t="n">
         <v>1.59</v>
@@ -2492,13 +2492,13 @@
         <v>19</v>
       </c>
       <c r="AQ8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT8" t="n">
         <v>9</v>
@@ -2510,7 +2510,7 @@
         <v>20</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX8" t="n">
         <v>9.199999999999999</v>
@@ -2534,13 +2534,13 @@
         <v>18</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF8" t="n">
         <v>5.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G9" t="n">
         <v>1.56</v>
@@ -2644,13 +2644,13 @@
         <v>7.6</v>
       </c>
       <c r="I9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
         <v>4.3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.41</v>
@@ -2665,22 +2665,22 @@
         <v>1.32</v>
       </c>
       <c r="P9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1.96</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1.97</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
         <v>3.55</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V9" t="n">
         <v>1.14</v>
@@ -2701,10 +2701,10 @@
         <v>700</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD9" t="n">
         <v>36</v>
@@ -2713,10 +2713,10 @@
         <v>700</v>
       </c>
       <c r="AF9" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AG9" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH9" t="n">
         <v>75</v>
@@ -2743,67 +2743,67 @@
         <v>180</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="AQ9" t="n">
         <v>17.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.6</v>
+        <v>27</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT9" t="n">
         <v>6.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AV9" t="n">
         <v>20</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.1</v>
+        <v>9.4</v>
       </c>
       <c r="AX9" t="n">
         <v>7.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC9" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD9" t="n">
         <v>26</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.2</v>
+        <v>9.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK9" t="n">
         <v>5.5</v>
@@ -2812,13 +2812,13 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN9" t="n">
         <v>4.1</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BP9" t="n">
         <v>10.5</v>
@@ -2833,10 +2833,10 @@
         <v>7.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
@@ -2848,7 +2848,7 @@
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -2889,46 +2889,46 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="G10" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H10" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O10" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="T10" t="n">
         <v>1.67</v>
@@ -2937,28 +2937,28 @@
         <v>1.92</v>
       </c>
       <c r="V10" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W10" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="X10" t="n">
         <v>24</v>
       </c>
       <c r="Y10" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Z10" t="n">
         <v>55</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB10" t="n">
         <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD10" t="n">
         <v>27</v>
@@ -2970,7 +2970,7 @@
         <v>13</v>
       </c>
       <c r="AG10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
         <v>24</v>
@@ -2979,10 +2979,10 @@
         <v>85</v>
       </c>
       <c r="AJ10" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL10" t="n">
         <v>36</v>
@@ -2991,22 +2991,22 @@
         <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO10" t="n">
         <v>110</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AT10" t="n">
         <v>7.6</v>
@@ -3015,22 +3015,22 @@
         <v>8</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY10" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB10" t="n">
         <v>11.5</v>
@@ -3039,16 +3039,16 @@
         <v>12</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="BH10" t="n">
         <v>4.1</v>
@@ -3078,7 +3078,7 @@
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -3143,76 +3143,76 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
         <v>2.14</v>
       </c>
-      <c r="G11" t="n">
-        <v>2.34</v>
-      </c>
       <c r="H11" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="J11" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O11" t="n">
         <v>1.34</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T11" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U11" t="n">
         <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="X11" t="n">
         <v>15.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA11" t="n">
         <v>85</v>
       </c>
       <c r="AB11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD11" t="n">
         <v>18</v>
@@ -3221,10 +3221,10 @@
         <v>55</v>
       </c>
       <c r="AF11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
         <v>21</v>
@@ -3233,19 +3233,19 @@
         <v>65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL11" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM11" t="n">
         <v>120</v>
       </c>
       <c r="AN11" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AO11" t="n">
         <v>60</v>
@@ -3254,31 +3254,31 @@
         <v>10</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
         <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU11" t="n">
         <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW11" t="n">
         <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AZ11" t="n">
         <v>14</v>
@@ -3287,10 +3287,10 @@
         <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BD11" t="n">
         <v>1.03</v>
@@ -3299,16 +3299,16 @@
         <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BG11" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BJ11" t="n">
         <v>10.5</v>
@@ -3323,50 +3323,50 @@
         <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BO11" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BP11" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BT11" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G12" t="n">
         <v>1.62</v>
       </c>
       <c r="H12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I12" t="n">
         <v>7</v>
@@ -3421,25 +3421,25 @@
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
         <v>1.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="R12" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S12" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="T12" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U12" t="n">
         <v>2.14</v>
@@ -3448,10 +3448,10 @@
         <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Y12" t="n">
         <v>29</v>
@@ -3484,10 +3484,10 @@
         <v>21</v>
       </c>
       <c r="AI12" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK12" t="n">
         <v>16.5</v>
@@ -3505,10 +3505,10 @@
         <v>85</v>
       </c>
       <c r="AP12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AR12" t="n">
         <v>1.03</v>
@@ -3517,25 +3517,25 @@
         <v>1.03</v>
       </c>
       <c r="AT12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU12" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AU12" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AV12" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
         <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
         <v>1.03</v>
@@ -3544,25 +3544,25 @@
         <v>11</v>
       </c>
       <c r="BC12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BD12" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
         <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BG12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BH12" t="n">
         <v>4.5</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="BJ12" t="n">
         <v>10.5</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="G2" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="I2" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>1.37</v>
@@ -887,190 +887,190 @@
         <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R2" t="n">
         <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U2" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V2" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="X2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y2" t="n">
         <v>15.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB2" t="n">
         <v>12</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AF2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG2" t="n">
         <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AJ2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AK2" t="n">
         <v>24</v>
       </c>
       <c r="AL2" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AM2" t="n">
-        <v>380</v>
+        <v>85</v>
       </c>
       <c r="AN2" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AP2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS2" t="n">
         <v>50</v>
       </c>
       <c r="AT2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY2" t="n">
         <v>10</v>
       </c>
-      <c r="AU2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW2" t="n">
+      <c r="AZ2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB2" t="n">
         <v>27</v>
       </c>
-      <c r="AX2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB2" t="n">
+      <c r="BC2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>60</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG2" t="n">
         <v>25</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>40</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>23</v>
       </c>
       <c r="BH2" t="n">
         <v>3.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU2" t="n">
         <v>5.5</v>
       </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -1114,22 +1114,22 @@
         <v>1.54</v>
       </c>
       <c r="G3" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="H3" t="n">
         <v>7.2</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
@@ -1138,13 +1138,13 @@
         <v>3.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
         <v>1.32</v>
@@ -1153,16 +1153,16 @@
         <v>3.75</v>
       </c>
       <c r="T3" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="U3" t="n">
         <v>1.78</v>
       </c>
       <c r="V3" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W3" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="X3" t="n">
         <v>14</v>
@@ -1171,10 +1171,10 @@
         <v>22</v>
       </c>
       <c r="Z3" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AA3" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AB3" t="n">
         <v>7.4</v>
@@ -1186,40 +1186,40 @@
         <v>29</v>
       </c>
       <c r="AE3" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH3" t="n">
         <v>27</v>
       </c>
       <c r="AI3" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AJ3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM3" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN3" t="n">
         <v>10.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AP3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>19</v>
@@ -1228,10 +1228,10 @@
         <v>50</v>
       </c>
       <c r="AS3" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU3" t="n">
         <v>8.800000000000001</v>
@@ -1264,67 +1264,67 @@
         <v>36</v>
       </c>
       <c r="BE3" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BF3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG3" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="BH3" t="n">
         <v>3.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BJ3" t="n">
         <v>12</v>
       </c>
       <c r="BK3" t="n">
-        <v>9.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN3" t="n">
         <v>4.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP3" t="n">
         <v>11</v>
       </c>
       <c r="BQ3" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="BR3" t="n">
         <v>32</v>
       </c>
       <c r="BS3" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="BT3" t="n">
         <v>11</v>
       </c>
       <c r="BU3" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="BV3" t="n">
         <v>75</v>
       </c>
       <c r="BW3" t="n">
-        <v>48</v>
+        <v>9.4</v>
       </c>
       <c r="BX3" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>50</v>
+        <v>9.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -1365,55 +1365,55 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="G4" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H4" t="n">
         <v>3.8</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
         <v>2.62</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R4" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="U4" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
         <v>2.02</v>
@@ -1431,19 +1431,19 @@
         <v>95</v>
       </c>
       <c r="AB4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
         <v>17</v>
       </c>
       <c r="AE4" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
@@ -1455,7 +1455,7 @@
         <v>70</v>
       </c>
       <c r="AJ4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AK4" t="n">
         <v>18</v>
@@ -1467,19 +1467,19 @@
         <v>320</v>
       </c>
       <c r="AN4" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AO4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AP4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AQ4" t="n">
         <v>19.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AS4" t="n">
         <v>16</v>
@@ -1488,25 +1488,25 @@
         <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW4" t="n">
         <v>32</v>
       </c>
       <c r="AX4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB4" t="n">
         <v>19.5</v>
@@ -1518,31 +1518,31 @@
         <v>22</v>
       </c>
       <c r="BE4" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF4" t="n">
         <v>7.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BJ4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN4" t="n">
         <v>5.2</v>
@@ -1554,16 +1554,16 @@
         <v>13</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR4" t="n">
         <v>22</v>
       </c>
       <c r="BS4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT4" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>8</v>
       </c>
       <c r="BU4" t="n">
         <v>5</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="G5" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="H5" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="J5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K5" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="P5" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="R5" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="S5" t="n">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="T5" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="U5" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="W5" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="X5" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="Y5" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI5" t="n">
         <v>48</v>
       </c>
-      <c r="Z5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>700</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AJ5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS5" t="n">
         <v>14.5</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AT5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA5" t="n">
         <v>24</v>
       </c>
-      <c r="AE5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>34</v>
-      </c>
       <c r="BB5" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>17.5</v>
+        <v>8.4</v>
       </c>
       <c r="BE5" t="n">
         <v>40</v>
       </c>
       <c r="BF5" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="BH5" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BN5" t="n">
         <v>5.9</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -1873,64 +1873,64 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G6" t="n">
         <v>2.84</v>
       </c>
       <c r="H6" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="I6" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="J6" t="n">
         <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P6" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="U6" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="V6" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X6" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z6" t="n">
         <v>24</v>
@@ -1939,49 +1939,49 @@
         <v>44</v>
       </c>
       <c r="AB6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF6" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AG6" t="n">
         <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM6" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="AN6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO6" t="n">
         <v>23</v>
       </c>
-      <c r="AO6" t="n">
-        <v>25</v>
-      </c>
       <c r="AP6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ6" t="n">
         <v>11</v>
@@ -1990,7 +1990,7 @@
         <v>17</v>
       </c>
       <c r="AS6" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AT6" t="n">
         <v>10.5</v>
@@ -2005,19 +2005,19 @@
         <v>22</v>
       </c>
       <c r="AX6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY6" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB6" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BC6" t="n">
         <v>21</v>
@@ -2026,31 +2026,31 @@
         <v>27</v>
       </c>
       <c r="BE6" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BF6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG6" t="n">
         <v>18.5</v>
       </c>
-      <c r="BG6" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BH6" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.4</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BN6" t="n">
         <v>6</v>
@@ -2059,16 +2059,16 @@
         <v>4.4</v>
       </c>
       <c r="BP6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BR6" t="n">
         <v>32</v>
       </c>
       <c r="BS6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BT6" t="n">
         <v>6.2</v>
@@ -2077,26 +2077,26 @@
         <v>4.5</v>
       </c>
       <c r="BV6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BX6" t="n">
         <v>32</v>
       </c>
       <c r="BY6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BZ6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J8" t="n">
         <v>4.3</v>
@@ -2423,16 +2423,16 @@
         <v>2.48</v>
       </c>
       <c r="T8" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U8" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="X8" t="n">
         <v>25</v>
@@ -2492,7 +2492,7 @@
         <v>19</v>
       </c>
       <c r="AQ8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR8" t="n">
         <v>8</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -2635,52 +2635,52 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="G9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H9" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9" t="n">
         <v>4.3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="U9" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="V9" t="n">
         <v>1.14</v>
@@ -2701,10 +2701,10 @@
         <v>700</v>
       </c>
       <c r="AB9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD9" t="n">
         <v>36</v>
@@ -2713,7 +2713,7 @@
         <v>700</v>
       </c>
       <c r="AF9" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG9" t="n">
         <v>10.5</v>
@@ -2731,16 +2731,16 @@
         <v>21</v>
       </c>
       <c r="AL9" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="AM9" t="n">
         <v>700</v>
       </c>
       <c r="AN9" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO9" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AP9" t="n">
         <v>7.4</v>
@@ -2749,106 +2749,106 @@
         <v>17.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU9" t="n">
         <v>8</v>
       </c>
       <c r="AV9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW9" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
         <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD9" t="n">
         <v>26</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN9" t="n">
         <v>4.1</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BP9" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT9" t="n">
         <v>11.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G10" t="n">
         <v>1.64</v>
@@ -2907,31 +2907,31 @@
         <v>4.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="T10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U10" t="n">
         <v>1.92</v>
@@ -2943,10 +2943,10 @@
         <v>2.52</v>
       </c>
       <c r="X10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y10" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Z10" t="n">
         <v>55</v>
@@ -2955,10 +2955,10 @@
         <v>200</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD10" t="n">
         <v>27</v>
@@ -2970,7 +2970,7 @@
         <v>13</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
         <v>24</v>
@@ -2997,31 +2997,31 @@
         <v>110</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.9</v>
+        <v>12.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS10" t="n">
         <v>4.8</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>5.2</v>
       </c>
       <c r="AT10" t="n">
         <v>7.6</v>
       </c>
       <c r="AU10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX10" t="n">
         <v>8</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="AY10" t="n">
         <v>7.6</v>
@@ -3030,25 +3030,25 @@
         <v>14.5</v>
       </c>
       <c r="BA10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC10" t="n">
         <v>5</v>
       </c>
-      <c r="BB10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>12</v>
-      </c>
       <c r="BD10" t="n">
-        <v>5.3</v>
+        <v>22</v>
       </c>
       <c r="BE10" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BH10" t="n">
         <v>4.1</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G11" t="n">
         <v>2.14</v>
@@ -3155,7 +3155,7 @@
         <v>4.3</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K11" t="n">
         <v>3.95</v>
@@ -3173,7 +3173,7 @@
         <v>1.34</v>
       </c>
       <c r="P11" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q11" t="n">
         <v>2.04</v>
@@ -3182,10 +3182,10 @@
         <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="T11" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="U11" t="n">
         <v>2</v>
@@ -3197,22 +3197,22 @@
         <v>1.87</v>
       </c>
       <c r="X11" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Z11" t="n">
         <v>30</v>
       </c>
       <c r="AA11" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD11" t="n">
         <v>18</v>
@@ -3221,16 +3221,16 @@
         <v>55</v>
       </c>
       <c r="AF11" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AJ11" t="n">
         <v>30</v>
@@ -3242,67 +3242,67 @@
         <v>44</v>
       </c>
       <c r="AM11" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AO11" t="n">
         <v>60</v>
       </c>
       <c r="AP11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ11" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AT11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU11" t="n">
         <v>6.8</v>
       </c>
-      <c r="AU11" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AV11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="AX11" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF11" t="n">
         <v>14</v>
       </c>
-      <c r="BA11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>13</v>
-      </c>
       <c r="BG11" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BH11" t="n">
         <v>3.45</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="G12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H12" t="n">
         <v>5.6</v>
@@ -3436,10 +3436,10 @@
         <v>1.58</v>
       </c>
       <c r="S12" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U12" t="n">
         <v>2.14</v>
@@ -3448,13 +3448,13 @@
         <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="X12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Z12" t="n">
         <v>65</v>
@@ -3463,10 +3463,10 @@
         <v>180</v>
       </c>
       <c r="AB12" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD12" t="n">
         <v>30</v>
@@ -3475,7 +3475,7 @@
         <v>90</v>
       </c>
       <c r="AF12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG12" t="n">
         <v>12.5</v>
@@ -3487,13 +3487,13 @@
         <v>80</v>
       </c>
       <c r="AJ12" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -3517,25 +3517,25 @@
         <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AU12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AW12" t="n">
         <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY12" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="n">
         <v>1.03</v>
@@ -3544,10 +3544,10 @@
         <v>11</v>
       </c>
       <c r="BC12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BE12" t="n">
         <v>1.03</v>
@@ -3556,7 +3556,7 @@
         <v>5</v>
       </c>
       <c r="BG12" t="n">
-        <v>48</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH12" t="n">
         <v>4.5</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -857,220 +857,220 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.36</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>2.42</v>
+        <v>90</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2</v>
+        <v>1.21</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3</v>
+        <v>1.24</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>6.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.43</v>
+        <v>4.9</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AT2" t="n">
         <v>65</v>
       </c>
-      <c r="AB2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AU2" t="n">
-        <v>7.6</v>
+        <v>110</v>
       </c>
       <c r="AV2" t="n">
-        <v>12</v>
+        <v>1.52</v>
       </c>
       <c r="AW2" t="n">
-        <v>30</v>
+        <v>7.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>14.5</v>
+        <v>250</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14.5</v>
+        <v>5.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="BB2" t="n">
-        <v>27</v>
+        <v>250</v>
       </c>
       <c r="BC2" t="n">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="BD2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BE2" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="BF2" t="n">
-        <v>15.5</v>
+        <v>140</v>
       </c>
       <c r="BG2" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -1111,115 +1111,115 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H3" t="n">
         <v>7.2</v>
       </c>
       <c r="I3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J3" t="n">
         <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="O3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.36</v>
       </c>
-      <c r="P3" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.32</v>
-      </c>
       <c r="S3" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="V3" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W3" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X3" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Y3" t="n">
         <v>22</v>
       </c>
       <c r="Z3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA3" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AB3" t="n">
         <v>7.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE3" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG3" t="n">
         <v>9.6</v>
       </c>
       <c r="AH3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AJ3" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK3" t="n">
         <v>18.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO3" t="n">
         <v>200</v>
       </c>
       <c r="AP3" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AQ3" t="n">
         <v>19</v>
@@ -1228,67 +1228,67 @@
         <v>50</v>
       </c>
       <c r="AS3" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW3" t="n">
         <v>60</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
         <v>22</v>
       </c>
       <c r="BA3" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="BB3" t="n">
         <v>12.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="BJ3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.7</v>
+        <v>9.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN3" t="n">
         <v>4.1</v>
@@ -1297,13 +1297,13 @@
         <v>3.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="BR3" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BS3" t="n">
         <v>8</v>
@@ -1312,19 +1312,19 @@
         <v>11</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV3" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -1365,58 +1365,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="G4" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="H4" t="n">
         <v>3.8</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J4" t="n">
         <v>4.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.27</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P4" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U4" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.56</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
         <v>24</v>
@@ -1434,13 +1434,13 @@
         <v>15</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD4" t="n">
         <v>17</v>
       </c>
       <c r="AE4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF4" t="n">
         <v>16</v>
@@ -1449,67 +1449,67 @@
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL4" t="n">
         <v>26</v>
       </c>
       <c r="AM4" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AO4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP4" t="n">
         <v>22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AR4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AS4" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="AT4" t="n">
         <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV4" t="n">
         <v>14.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX4" t="n">
         <v>13.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
         <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB4" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="n">
         <v>15</v>
@@ -1518,16 +1518,16 @@
         <v>22</v>
       </c>
       <c r="BE4" t="n">
-        <v>11.5</v>
+        <v>48</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI4" t="n">
         <v>4.1</v>
@@ -1536,13 +1536,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN4" t="n">
         <v>5.2</v>
@@ -1554,13 +1554,13 @@
         <v>13</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT4" t="n">
         <v>7.8</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H5" t="n">
         <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="J5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
         <v>1.16</v>
@@ -1643,28 +1643,28 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="P5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="R5" t="n">
         <v>2.38</v>
       </c>
       <c r="S5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="T5" t="n">
         <v>1.38</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="V5" t="n">
         <v>1.15</v>
@@ -1673,176 +1673,176 @@
         <v>3</v>
       </c>
       <c r="X5" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="Y5" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="Z5" t="n">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="AA5" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB5" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="AC5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AD5" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AE5" t="n">
         <v>75</v>
       </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>500</v>
       </c>
       <c r="AG5" t="n">
         <v>14</v>
       </c>
       <c r="AH5" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AO5" t="n">
         <v>34</v>
       </c>
-      <c r="AK5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>32</v>
-      </c>
       <c r="AP5" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AQ5" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="AR5" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AS5" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT5" t="n">
         <v>21</v>
       </c>
       <c r="AU5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AV5" t="n">
         <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>12.5</v>
+        <v>55</v>
       </c>
       <c r="AX5" t="n">
         <v>14.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="BB5" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE5" t="n">
         <v>40</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="BG5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BH5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BI5" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BN5" t="n">
         <v>5.9</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BU5" t="n">
         <v>5.1</v>
       </c>
-      <c r="BT5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BZ5" t="n">
         <v>7.2</v>
       </c>
       <c r="CA5" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="G6" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I6" t="n">
         <v>2.94</v>
@@ -1891,28 +1891,28 @@
         <v>3.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="T6" t="n">
         <v>1.6</v>
@@ -1924,28 +1924,28 @@
         <v>1.52</v>
       </c>
       <c r="W6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X6" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="n">
         <v>14</v>
       </c>
-      <c r="Z6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
         <v>29</v>
@@ -1957,7 +1957,7 @@
         <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI6" t="n">
         <v>38</v>
@@ -1972,28 +1972,28 @@
         <v>38</v>
       </c>
       <c r="AM6" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO6" t="n">
         <v>22</v>
       </c>
-      <c r="AO6" t="n">
-        <v>23</v>
-      </c>
       <c r="AP6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS6" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AT6" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU6" t="n">
         <v>7.2</v>
@@ -2014,13 +2014,13 @@
         <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB6" t="n">
         <v>32</v>
       </c>
       <c r="BC6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD6" t="n">
         <v>27</v>
@@ -2029,19 +2029,19 @@
         <v>34</v>
       </c>
       <c r="BF6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK6" t="n">
         <v>6.6</v>
@@ -2065,7 +2065,7 @@
         <v>14</v>
       </c>
       <c r="BR6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS6" t="n">
         <v>21</v>
@@ -2089,14 +2089,14 @@
         <v>21</v>
       </c>
       <c r="BZ6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA6" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -2426,13 +2426,13 @@
         <v>1.71</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V8" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W8" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X8" t="n">
         <v>25</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -2641,37 +2641,37 @@
         <v>1.55</v>
       </c>
       <c r="H9" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="I9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q9" t="n">
         <v>1.9</v>
       </c>
       <c r="R9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
         <v>3.25</v>
@@ -2680,16 +2680,16 @@
         <v>1.98</v>
       </c>
       <c r="U9" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="V9" t="n">
         <v>1.14</v>
       </c>
       <c r="W9" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="X9" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="Y9" t="n">
         <v>28</v>
@@ -2725,140 +2725,140 @@
         <v>700</v>
       </c>
       <c r="AJ9" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AK9" t="n">
         <v>21</v>
       </c>
       <c r="AL9" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="AM9" t="n">
         <v>700</v>
       </c>
       <c r="AN9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AO9" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AP9" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="AQ9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR9" t="n">
         <v>42</v>
       </c>
       <c r="AS9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT9" t="n">
         <v>7</v>
       </c>
       <c r="AU9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY9" t="n">
         <v>8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
         <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.800000000000001</v>
+        <v>44</v>
       </c>
       <c r="BB9" t="n">
         <v>11.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD9" t="n">
         <v>26</v>
       </c>
       <c r="BE9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI9" t="n">
         <v>3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BN9" t="n">
         <v>4.1</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="BP9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H10" t="n">
         <v>6</v>
@@ -2901,49 +2901,49 @@
         <v>7.2</v>
       </c>
       <c r="J10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="R10" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="U10" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V10" t="n">
         <v>1.16</v>
       </c>
       <c r="W10" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X10" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="Y10" t="n">
         <v>25</v>
@@ -2952,109 +2952,109 @@
         <v>55</v>
       </c>
       <c r="AA10" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE10" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AF10" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI10" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AJ10" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AK10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL10" t="n">
         <v>36</v>
       </c>
       <c r="AM10" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AO10" t="n">
         <v>110</v>
       </c>
       <c r="AP10" t="n">
-        <v>12.5</v>
+        <v>5.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>20</v>
+        <v>6.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AW10" t="n">
         <v>5.7</v>
       </c>
       <c r="AX10" t="n">
-        <v>8</v>
+        <v>4.7</v>
       </c>
       <c r="AY10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE10" t="n">
         <v>7.6</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BF10" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BG10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BH10" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
@@ -3075,22 +3075,22 @@
         <v>3.3</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
@@ -3108,11 +3108,11 @@
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -3176,16 +3176,16 @@
         <v>1.86</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R11" t="n">
         <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T11" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U11" t="n">
         <v>2</v>
@@ -3206,7 +3206,7 @@
         <v>30</v>
       </c>
       <c r="AA11" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB11" t="n">
         <v>9.4</v>
@@ -3230,13 +3230,13 @@
         <v>20</v>
       </c>
       <c r="AI11" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ11" t="n">
         <v>30</v>
       </c>
       <c r="AK11" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL11" t="n">
         <v>44</v>
@@ -3245,7 +3245,7 @@
         <v>150</v>
       </c>
       <c r="AN11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO11" t="n">
         <v>60</v>
@@ -3260,7 +3260,7 @@
         <v>22</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT11" t="n">
         <v>7.4</v>
@@ -3272,7 +3272,7 @@
         <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX11" t="n">
         <v>10.5</v>
@@ -3296,7 +3296,7 @@
         <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF11" t="n">
         <v>14</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -3400,13 +3400,13 @@
         <v>1.58</v>
       </c>
       <c r="G12" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H12" t="n">
         <v>5.6</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J12" t="n">
         <v>4.4</v>
@@ -3421,22 +3421,22 @@
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O12" t="n">
         <v>1.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R12" t="n">
         <v>1.58</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T12" t="n">
         <v>1.7</v>
@@ -3448,7 +3448,7 @@
         <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X12" t="n">
         <v>29</v>
@@ -3505,58 +3505,58 @@
         <v>85</v>
       </c>
       <c r="AP12" t="n">
-        <v>17</v>
+        <v>4.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT12" t="n">
         <v>9.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX12" t="n">
         <v>9.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB12" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BC12" t="n">
         <v>13</v>
       </c>
       <c r="BD12" t="n">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF12" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="BH12" t="n">
         <v>4.5</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB12"/>
+  <dimension ref="A1:CB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,36 +843,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FK Tukums 2000</t>
+          <t>Forge</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SK Super Nova</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>2.32</v>
       </c>
       <c r="G2" t="n">
-        <v>90</v>
+        <v>2.34</v>
       </c>
       <c r="H2" t="n">
-        <v>1.21</v>
+        <v>7.8</v>
       </c>
       <c r="I2" t="n">
-        <v>1.24</v>
+        <v>8</v>
       </c>
       <c r="J2" t="n">
-        <v>5.4</v>
+        <v>2.22</v>
       </c>
       <c r="K2" t="n">
-        <v>6.4</v>
+        <v>2.24</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -893,10 +893,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>4.7</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -929,10 +929,10 @@
         <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.6</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
@@ -941,10 +941,10 @@
         <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
@@ -953,16 +953,16 @@
         <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AN2" t="n">
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
         <v>250</v>
@@ -977,46 +977,46 @@
         <v>250</v>
       </c>
       <c r="AT2" t="n">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="AU2" t="n">
-        <v>110</v>
+        <v>250</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AX2" t="n">
         <v>250</v>
       </c>
       <c r="AY2" t="n">
-        <v>110</v>
+        <v>250</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
         <v>250</v>
       </c>
       <c r="BC2" t="n">
-        <v>110</v>
+        <v>250</v>
       </c>
       <c r="BD2" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>140</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1102,229 +1102,229 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Forge</t>
+          <t>Eskilsminne</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Kristianstads</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.57</v>
+        <v>1.15</v>
       </c>
       <c r="G3" t="n">
-        <v>1.59</v>
+        <v>1.16</v>
       </c>
       <c r="H3" t="n">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="I3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J3" t="n">
         <v>7.6</v>
       </c>
-      <c r="J3" t="n">
-        <v>4.2</v>
-      </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>250</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>250</v>
+      </c>
+      <c r="BD3" t="n">
         <v>1.15</v>
       </c>
-      <c r="W3" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="X3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>250</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF3" t="n">
+      <c r="BE3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AG3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>85</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>85</v>
-      </c>
       <c r="BF3" t="n">
-        <v>8.4</v>
+        <v>4.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>80</v>
+        <v>4.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Eskilsminne</t>
+          <t>Haukar</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kristianstads</t>
+          <t>Kari</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="G4" t="n">
-        <v>1.99</v>
+        <v>1.47</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="I4" t="n">
-        <v>3.95</v>
+        <v>7.4</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="P4" t="n">
-        <v>2.68</v>
+        <v>4.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.54</v>
+        <v>1.24</v>
       </c>
       <c r="R4" t="n">
-        <v>1.68</v>
+        <v>2.56</v>
       </c>
       <c r="S4" t="n">
-        <v>2.34</v>
+        <v>1.59</v>
       </c>
       <c r="T4" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="U4" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="X4" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="Y4" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL4" t="n">
         <v>23</v>
       </c>
-      <c r="Z4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="AM4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX4" t="n">
         <v>15</v>
       </c>
-      <c r="AC4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF4" t="n">
+      <c r="AY4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB4" t="n">
         <v>16</v>
       </c>
-      <c r="AG4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW4" t="n">
+      <c r="BC4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE4" t="n">
         <v>34</v>
       </c>
-      <c r="AX4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>48</v>
-      </c>
       <c r="BF4" t="n">
-        <v>7.6</v>
+        <v>3.05</v>
       </c>
       <c r="BG4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="BJ4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BK4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BN4" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BO4" t="n">
         <v>4.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR4" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="BZ4" t="n">
-        <v>15.5</v>
+        <v>7</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,153 +1605,153 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Haukar</t>
+          <t>HFX Wanderers</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kari</t>
+          <t>Atletico Ottawa</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="G5" t="n">
-        <v>1.49</v>
+        <v>2.8</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>2.74</v>
       </c>
       <c r="I5" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC5" t="n">
         <v>8.6</v>
       </c>
-      <c r="J5" t="n">
-        <v>5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>6</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="P5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W5" t="n">
-        <v>3</v>
-      </c>
-      <c r="X5" t="n">
-        <v>95</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>80</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>140</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>210</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>22</v>
-      </c>
       <c r="AD5" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="AF5" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AI5" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="AK5" t="n">
-        <v>13.5</v>
+        <v>28</v>
       </c>
       <c r="AL5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN5" t="n">
         <v>21</v>
       </c>
-      <c r="AM5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AO5" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AP5" t="n">
-        <v>50</v>
+        <v>14.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW5" t="n">
         <v>24</v>
       </c>
-      <c r="AS5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>55</v>
-      </c>
       <c r="AX5" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AY5" t="n">
         <v>10.5</v>
@@ -1760,96 +1760,96 @@
         <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BB5" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>16</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>24</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>25</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>23</v>
+      </c>
+      <c r="CA5" t="n">
         <v>15.5</v>
       </c>
-      <c r="BC5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>40</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>25</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>5.5</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,246 +1864,246 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Atletico Ottawa</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="G6" t="n">
-        <v>2.78</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="I6" t="n">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="O6" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="S6" t="n">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,180 +2113,180 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Charlotte Independence</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Corpus Christi</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>1.6</v>
       </c>
       <c r="H7" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>2.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="R7" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="S7" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Charlotte Independence</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Corpus Christi</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="G8" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="I8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="X8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>170</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>700</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX8" t="n">
         <v>7.2</v>
       </c>
-      <c r="J8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X8" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>50</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>180</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AY8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB8" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="BC8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ8" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD8" t="n">
-        <v>48</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>400</v>
-      </c>
-      <c r="AF8" t="n">
+      <c r="BK8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT8" t="n">
         <v>11.5</v>
       </c>
-      <c r="AG8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>320</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT8" t="n">
+      <c r="BU8" t="n">
         <v>9</v>
       </c>
-      <c r="AU8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB8" t="n">
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="CA8" t="n">
         <v>12.5</v>
       </c>
-      <c r="BC8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,207 +2621,207 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Chattanooga Red Wolves SC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Westchester SC</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="H9" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="M9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P9" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="T9" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="U9" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="V9" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W9" t="n">
-        <v>2.82</v>
+        <v>2.52</v>
       </c>
       <c r="X9" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="Y9" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Z9" t="n">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="AA9" t="n">
-        <v>700</v>
+        <v>210</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AC9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG9" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AH9" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="AI9" t="n">
-        <v>700</v>
+        <v>110</v>
       </c>
       <c r="AJ9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AK9" t="n">
         <v>21</v>
       </c>
       <c r="AL9" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="AM9" t="n">
-        <v>700</v>
+        <v>180</v>
       </c>
       <c r="AN9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE9" t="n">
         <v>8.4</v>
       </c>
-      <c r="AO9" t="n">
-        <v>180</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW9" t="n">
+      <c r="BF9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ9" t="n">
         <v>10.5</v>
       </c>
-      <c r="AX9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>12</v>
-      </c>
       <c r="BK9" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="BP9" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
         <v>7.4</v>
@@ -2830,35 +2830,35 @@
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
         <v>7.2</v>
       </c>
-      <c r="BT9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="BZ9" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
@@ -2875,244 +2875,244 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>23:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Chattanooga Red Wolves SC</t>
+          <t>Spokane Velocity FC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Westchester SC</t>
+          <t>Forward Madison FC</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>1.65</v>
+        <v>2.14</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="I10" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="J10" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="O10" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="P10" t="n">
-        <v>2.12</v>
+        <v>1.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="T10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W10" t="n">
         <v>1.87</v>
       </c>
-      <c r="U10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.5</v>
-      </c>
       <c r="X10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD10" t="n">
         <v>18</v>
       </c>
-      <c r="Y10" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>210</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>25</v>
-      </c>
       <c r="AE10" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AF10" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ10" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AK10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB10" t="n">
         <v>21</v>
       </c>
-      <c r="AL10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP10" t="n">
+      <c r="BC10" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU10" t="n">
         <v>5.6</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
@@ -3129,228 +3129,228 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>23:00:00</t>
+          <t>23:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Spokane Velocity FC</t>
+          <t>Union Omaha</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Forward Madison FC</t>
+          <t>AV Alta FC</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="G11" t="n">
-        <v>2.14</v>
+        <v>1.65</v>
       </c>
       <c r="H11" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="I11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J11" t="n">
         <v>4.3</v>
       </c>
-      <c r="J11" t="n">
-        <v>3.45</v>
-      </c>
       <c r="K11" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>3.55</v>
+        <v>5.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="P11" t="n">
-        <v>1.86</v>
+        <v>2.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="S11" t="n">
-        <v>3.65</v>
+        <v>2.46</v>
       </c>
       <c r="T11" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="W11" t="n">
-        <v>1.87</v>
+        <v>2.52</v>
       </c>
       <c r="X11" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="Y11" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="Z11" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="AA11" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE11" t="n">
         <v>110</v>
       </c>
-      <c r="AB11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>55</v>
-      </c>
       <c r="AF11" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG11" t="n">
         <v>11</v>
       </c>
       <c r="AH11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>20</v>
       </c>
-      <c r="AI11" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AR11" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AW11" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AX11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BB11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD11" t="n">
         <v>21</v>
       </c>
-      <c r="BC11" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD11" t="n">
+      <c r="BE11" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BG11" t="n">
         <v>30</v>
       </c>
-      <c r="BE11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>32</v>
-      </c>
       <c r="BH11" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="BJ11" t="n">
         <v>10.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BN11" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="BP11" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS11" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="BT11" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
@@ -3359,268 +3359,14 @@
         <v>32</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>US USL League One</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>23:30:00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Union Omaha</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AV Alta FC</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="X12" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>180</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>65</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>22</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>15</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>32</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>32</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>10</v>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB11"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,180 +843,180 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Forge</t>
+          <t>Haukar</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Kari</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="G2" t="n">
-        <v>2.34</v>
+        <v>1.02</v>
       </c>
       <c r="H2" t="n">
+        <v>150</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>50</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA2" t="n">
         <v>7.8</v>
       </c>
-      <c r="I2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>900</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>990</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>250</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>250</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>250</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>250</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>250</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>250</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>250</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>250</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BB2" t="n">
-        <v>250</v>
+        <v>7.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>250</v>
+        <v>1.46</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,97 +1097,97 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Eskilsminne</t>
+          <t>HFX Wanderers</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kristianstads</t>
+          <t>Atletico Ottawa</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.15</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
+        <v>85</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="J3" t="n">
+        <v>19</v>
+      </c>
+      <c r="K3" t="n">
+        <v>23</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="S3" t="n">
         <v>1.16</v>
       </c>
-      <c r="H3" t="n">
-        <v>32</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="K3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
         <v>6.8</v>
       </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
       <c r="AF3" t="n">
         <v>1000</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
@@ -1207,70 +1207,70 @@
         <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.3</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>1.88</v>
       </c>
       <c r="AP3" t="n">
-        <v>250</v>
+        <v>19.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>250</v>
+        <v>18.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>250</v>
+        <v>16.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>250</v>
+        <v>6.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>250</v>
+        <v>19.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>250</v>
+        <v>18.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>250</v>
+        <v>16.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>250</v>
+        <v>5.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>250</v>
+        <v>19.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>250</v>
+        <v>18.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="BB3" t="n">
-        <v>250</v>
+        <v>19.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>250</v>
+        <v>18.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.15</v>
+        <v>16.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.7</v>
+        <v>65</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Haukar</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kari</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="G4" t="n">
-        <v>1.47</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="I4" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="O4" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>4.7</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="S4" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="T4" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,186 +1605,186 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Charlotte Independence</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Atletico Ottawa</t>
+          <t>Corpus Christi</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P5" t="n">
         <v>2.6</v>
       </c>
-      <c r="G5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.12</v>
-      </c>
       <c r="Q5" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="T5" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="U5" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="V5" t="n">
-        <v>1.51</v>
+        <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>1.56</v>
+        <v>2.28</v>
       </c>
       <c r="X5" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH5" t="n">
         <v>17.5</v>
       </c>
-      <c r="Y5" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AI5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>22</v>
       </c>
-      <c r="AA5" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ5" t="n">
+      <c r="AR5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW5" t="n">
         <v>44</v>
       </c>
-      <c r="AK5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL5" t="n">
+      <c r="AX5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA5" t="n">
         <v>36</v>
       </c>
-      <c r="AM5" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>30</v>
-      </c>
       <c r="BB5" t="n">
-        <v>28</v>
+        <v>16.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BD5" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="BE5" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="BF5" t="n">
-        <v>17.5</v>
+        <v>6.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="BJ5" t="n">
         <v>9.199999999999999</v>
@@ -1796,53 +1796,53 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN5" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>16</v>
+        <v>7.8</v>
       </c>
       <c r="BR5" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BS5" t="n">
-        <v>24</v>
+        <v>7.6</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BV5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>16.5</v>
+        <v>8.4</v>
       </c>
       <c r="BX5" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>25</v>
+        <v>8.6</v>
       </c>
       <c r="BZ5" t="n">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -1859,244 +1859,244 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>1.55</v>
       </c>
       <c r="H6" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>2.04</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="R6" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -2113,96 +2113,96 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Charlotte Independence</t>
+          <t>Chattanooga Red Wolves SC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Corpus Christi</t>
+          <t>Westchester SC</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="H7" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="I7" t="n">
         <v>7.4</v>
       </c>
       <c r="J7" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K7" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M7" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.64</v>
+        <v>2.18</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="R7" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="S7" t="n">
-        <v>2.34</v>
+        <v>2.86</v>
       </c>
       <c r="T7" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="U7" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="V7" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W7" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="X7" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Y7" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="Z7" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AA7" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AB7" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC7" t="n">
         <v>12.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE7" t="n">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="AF7" t="n">
         <v>12</v>
@@ -2211,153 +2211,153 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AJ7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK7" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AL7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA7" t="n">
         <v>44</v>
       </c>
-      <c r="AM7" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU7" t="n">
+      <c r="BB7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE7" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AV7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>28</v>
-      </c>
       <c r="BF7" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BG7" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,244 +2367,244 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>23:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Spokane Velocity FC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Forward Madison FC</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.51</v>
+        <v>1.96</v>
       </c>
       <c r="G8" t="n">
-        <v>1.56</v>
+        <v>2.14</v>
       </c>
       <c r="H8" t="n">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="L8" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="P8" t="n">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="T8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U8" t="n">
         <v>2</v>
       </c>
-      <c r="U8" t="n">
-        <v>1.85</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>2.78</v>
+        <v>1.88</v>
       </c>
       <c r="X8" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="Z8" t="n">
-        <v>170</v>
+        <v>32</v>
       </c>
       <c r="AA8" t="n">
-        <v>700</v>
+        <v>110</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG8" t="n">
         <v>11</v>
       </c>
-      <c r="AD8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AH8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AI8" t="n">
-        <v>700</v>
+        <v>110</v>
       </c>
       <c r="AJ8" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AK8" t="n">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="AL8" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AM8" t="n">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="AO8" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AP8" t="n">
         <v>11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>19</v>
+        <v>12.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU8" t="n">
         <v>6.8</v>
       </c>
-      <c r="AU8" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AV8" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="AX8" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="AY8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA8" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BF8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>11.5</v>
       </c>
-      <c r="BC8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.8</v>
+        <v>22</v>
       </c>
       <c r="BT8" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="BU8" t="n">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="BZ8" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -2621,752 +2621,244 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>23:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Chattanooga Red Wolves SC</t>
+          <t>Union Omaha</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Westchester SC</t>
+          <t>AV Alta FC</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G9" t="n">
         <v>1.65</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="I9" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="M9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="P9" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>2.94</v>
+        <v>2.48</v>
       </c>
       <c r="T9" t="n">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="U9" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="W9" t="n">
         <v>2.52</v>
       </c>
       <c r="X9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y9" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="Z9" t="n">
         <v>80</v>
       </c>
       <c r="AA9" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="AB9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG9" t="n">
         <v>11</v>
       </c>
-      <c r="AC9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AH9" t="n">
-        <v>27</v>
+        <v>19.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AJ9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK9" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AL9" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM9" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="AN9" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="AO9" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AP9" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="AS9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AV9" t="n">
         <v>18</v>
       </c>
       <c r="AW9" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AY9" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA9" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="BB9" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.6</v>
+        <v>21</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.4</v>
+        <v>55</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BG9" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS9" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>US USL League One</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>23:00:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Spokane Velocity FC</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Forward Madison FC</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="X10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>30</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>22</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>25</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>32</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>20</v>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>2026-07-01 15:52:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>US USL League One</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>23:30:00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Union Omaha</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AV Alta FC</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="H11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="I11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K11" t="n">
-        <v>5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="X11" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>30</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>30</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>65</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>22</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>30</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>32</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>10</v>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,72 +843,72 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Haukar</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kari</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1.01</v>
       </c>
       <c r="G2" t="n">
-        <v>1.02</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>150</v>
+        <v>1.01</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -950,144 +950,144 @@
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.82</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,36 +1097,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Charlotte Independence</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Atletico Ottawa</t>
+          <t>Corpus Christi</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>1.18</v>
       </c>
       <c r="G3" t="n">
-        <v>85</v>
+        <v>1.21</v>
       </c>
       <c r="H3" t="n">
-        <v>1.06</v>
+        <v>32</v>
       </c>
       <c r="I3" t="n">
-        <v>1.07</v>
+        <v>65</v>
       </c>
       <c r="J3" t="n">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="K3" t="n">
-        <v>23</v>
+        <v>7.6</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1147,131 +1147,131 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>6.6</v>
+        <v>3.25</v>
       </c>
       <c r="S3" t="n">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>15</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE3" t="n">
+      <c r="AR3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>6.8</v>
       </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>95</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AQ3" t="n">
+      <c r="BA3" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>250</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG3" t="n">
         <v>18.5</v>
       </c>
-      <c r="AR3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>25</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>65</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -1351,72 +1351,72 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>1.22</v>
       </c>
       <c r="H4" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.77</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="R4" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="S4" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1431,164 +1431,164 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>210</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>200</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>290</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Charlotte Independence</t>
+          <t>Chattanooga Red Wolves SC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Corpus Christi</t>
+          <t>Westchester SC</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="G5" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="H5" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="I5" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K5" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>2.42</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="U5" t="n">
-        <v>2.26</v>
+        <v>1.92</v>
       </c>
       <c r="V5" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="W5" t="n">
-        <v>2.28</v>
+        <v>2.76</v>
       </c>
       <c r="X5" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Z5" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AA5" t="n">
-        <v>700</v>
+        <v>340</v>
       </c>
       <c r="AB5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC5" t="n">
         <v>13</v>
       </c>
-      <c r="AC5" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AD5" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AE5" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AF5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG5" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>17.5</v>
+        <v>30</v>
       </c>
       <c r="AI5" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AK5" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AM5" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="AN5" t="n">
         <v>7.6</v>
       </c>
       <c r="AO5" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>960</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>80</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BX5" t="n">
         <v>75</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="BY5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BZ5" t="n">
         <v>19</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>19</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>48</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>32</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>27</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>13.5</v>
-      </c>
       <c r="CA5" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,244 +1859,244 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>23:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Spokane Velocity FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Forward Madison FC</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.54</v>
+        <v>1.98</v>
       </c>
       <c r="G6" t="n">
-        <v>1.55</v>
+        <v>2.16</v>
       </c>
       <c r="H6" t="n">
-        <v>7.2</v>
+        <v>3.85</v>
       </c>
       <c r="I6" t="n">
-        <v>7.8</v>
+        <v>4.5</v>
       </c>
       <c r="J6" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.89</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="W6" t="n">
-        <v>2.8</v>
+        <v>1.87</v>
       </c>
       <c r="X6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD6" t="n">
         <v>18</v>
       </c>
-      <c r="Y6" t="n">
-        <v>29</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>170</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>700</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="AE6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX6" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>700</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>180</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>7.4</v>
       </c>
       <c r="AY6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="BB6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ6" t="n">
         <v>11.5</v>
       </c>
-      <c r="BC6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="BT6" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="BZ6" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -2113,752 +2113,244 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>23:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Chattanooga Red Wolves SC</t>
+          <t>Union Omaha</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Westchester SC</t>
+          <t>AV Alta FC</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="G7" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="H7" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="I7" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K7" t="n">
         <v>4.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.18</v>
+        <v>2.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="S7" t="n">
-        <v>2.86</v>
+        <v>2.46</v>
       </c>
       <c r="T7" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="U7" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="V7" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W7" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="X7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y7" t="n">
         <v>32</v>
       </c>
       <c r="Z7" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA7" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF7" t="n">
         <v>12.5</v>
       </c>
-      <c r="AD7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>12</v>
-      </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>27</v>
+        <v>18.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK7" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM7" t="n">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="AO7" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AP7" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>18</v>
+        <v>6.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AS7" t="n">
         <v>7.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW7" t="n">
-        <v>48</v>
+        <v>7.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AY7" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>44</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>11</v>
+        <v>6.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="BG7" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="BJ7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK7" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BP7" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS7" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BT7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BU7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA7" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>US USL League One</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>23:00:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Spokane Velocity FC</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Forward Madison FC</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="X8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>30</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>22</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>25</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>32</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>20</v>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>2026-07-01 18:02:33</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>US USL League One</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>23:30:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Union Omaha</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AV Alta FC</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>5</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="X9" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>30</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>65</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>22</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>10</v>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
